--- a/research/traditional_assets/database/data/latvia/latvia_power.xlsx
+++ b/research/traditional_assets/database/data/latvia/latvia_power.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="rise_gze1r" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,43 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0254</v>
+        <v>0.182</v>
+      </c>
+      <c r="E2">
+        <v>0.487</v>
       </c>
       <c r="G2">
-        <v>0.08016339034975746</v>
+        <v>0.273084025854109</v>
       </c>
       <c r="H2">
-        <v>0.08016339034975746</v>
+        <v>0.273084025854109</v>
       </c>
       <c r="I2">
-        <v>-0.5151901965790145</v>
+        <v>0.3000923361034165</v>
       </c>
       <c r="J2">
-        <v>-0.5151901965790145</v>
+        <v>0.2987702430161397</v>
       </c>
       <c r="K2">
-        <v>-201.6</v>
+        <v>262.1</v>
       </c>
       <c r="L2">
-        <v>-0.5146796017360225</v>
+        <v>0.3025161588180979</v>
       </c>
       <c r="M2">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="N2">
-        <v>0.0258585022755482</v>
+        <v>0.03420689655172414</v>
       </c>
       <c r="O2">
-        <v>-0.06200396825396826</v>
+        <v>0.04731018695154521</v>
       </c>
       <c r="P2">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="Q2">
-        <v>0.0258585022755482</v>
+        <v>0.03420689655172414</v>
       </c>
       <c r="R2">
-        <v>-0.06200396825396826</v>
+        <v>0.04731018695154521</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>12.7</v>
+        <v>42.7</v>
       </c>
       <c r="V2">
-        <v>0.02627223831195697</v>
+        <v>0.1177931034482759</v>
       </c>
       <c r="W2">
-        <v>-0.4473041934768138</v>
+        <v>1.144541484716157</v>
       </c>
       <c r="X2">
-        <v>0.04707107857509037</v>
+        <v>0.0760733786790017</v>
       </c>
       <c r="Y2">
-        <v>-0.4943752720519042</v>
+        <v>1.068468106037155</v>
       </c>
       <c r="Z2">
-        <v>0.9539698002922553</v>
+        <v>2.864132231404958</v>
       </c>
       <c r="AA2">
-        <v>-0.4914758889430103</v>
+        <v>0.8557174828072179</v>
       </c>
       <c r="AB2">
-        <v>0.0440100736249114</v>
+        <v>0.07466159106993836</v>
       </c>
       <c r="AC2">
-        <v>-0.5354859625679217</v>
+        <v>0.7810558917372796</v>
       </c>
       <c r="AD2">
-        <v>86.2</v>
+        <v>20.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>86.2</v>
+        <v>20.4</v>
       </c>
       <c r="AG2">
-        <v>73.5</v>
+        <v>-22.3</v>
       </c>
       <c r="AH2">
-        <v>0.1513342696629214</v>
+        <v>0.05327761817706973</v>
       </c>
       <c r="AI2">
-        <v>0.2734771573604061</v>
+        <v>0.04410810810810811</v>
       </c>
       <c r="AJ2">
-        <v>0.1319806069312264</v>
+        <v>-0.06554967666078779</v>
       </c>
       <c r="AK2">
-        <v>0.2429752066115702</v>
+        <v>-0.05312053358742259</v>
       </c>
       <c r="AL2">
-        <v>0.228</v>
+        <v>0.746</v>
       </c>
       <c r="AM2">
-        <v>0.228</v>
+        <v>0.746</v>
       </c>
       <c r="AN2">
-        <v>-0.4634408602150538</v>
+        <v>0.07464324917672886</v>
       </c>
       <c r="AO2">
-        <v>-885.0877192982456</v>
+        <v>348.5254691689008</v>
       </c>
       <c r="AP2">
-        <v>-0.3951612903225806</v>
+        <v>-0.08159531650201245</v>
       </c>
       <c r="AQ2">
-        <v>-885.0877192982456</v>
+        <v>348.5254691689008</v>
       </c>
     </row>
     <row r="3">
@@ -719,43 +724,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0254</v>
+        <v>0.182</v>
+      </c>
+      <c r="E3">
+        <v>0.487</v>
       </c>
       <c r="G3">
-        <v>0.08016339034975746</v>
+        <v>0.273084025854109</v>
       </c>
       <c r="H3">
-        <v>0.08016339034975746</v>
+        <v>0.273084025854109</v>
       </c>
       <c r="I3">
-        <v>-0.5151901965790145</v>
+        <v>0.3000923361034165</v>
       </c>
       <c r="J3">
-        <v>-0.5151901965790145</v>
+        <v>0.2987702430161397</v>
       </c>
       <c r="K3">
-        <v>-201.6</v>
+        <v>262.1</v>
       </c>
       <c r="L3">
-        <v>-0.5146796017360225</v>
+        <v>0.3025161588180979</v>
       </c>
       <c r="M3">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="N3">
-        <v>0.0258585022755482</v>
+        <v>0.03420689655172414</v>
       </c>
       <c r="O3">
-        <v>-0.06200396825396826</v>
+        <v>0.04731018695154521</v>
       </c>
       <c r="P3">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="Q3">
-        <v>0.0258585022755482</v>
+        <v>0.03420689655172414</v>
       </c>
       <c r="R3">
-        <v>-0.06200396825396826</v>
+        <v>0.04731018695154521</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +772,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>12.7</v>
+        <v>42.7</v>
       </c>
       <c r="V3">
-        <v>0.02627223831195697</v>
+        <v>0.1177931034482759</v>
       </c>
       <c r="W3">
-        <v>-0.4473041934768138</v>
+        <v>1.144541484716157</v>
       </c>
       <c r="X3">
-        <v>0.04707107857509037</v>
+        <v>0.0760733786790017</v>
       </c>
       <c r="Y3">
-        <v>-0.4943752720519042</v>
+        <v>1.068468106037155</v>
       </c>
       <c r="Z3">
-        <v>0.9539698002922553</v>
+        <v>2.864132231404958</v>
       </c>
       <c r="AA3">
-        <v>-0.4914758889430103</v>
+        <v>0.8557174828072179</v>
       </c>
       <c r="AB3">
-        <v>0.0440100736249114</v>
+        <v>0.07466159106993836</v>
       </c>
       <c r="AC3">
-        <v>-0.5354859625679217</v>
+        <v>0.7810558917372796</v>
       </c>
       <c r="AD3">
-        <v>86.2</v>
+        <v>20.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>86.2</v>
+        <v>20.4</v>
       </c>
       <c r="AG3">
-        <v>73.5</v>
+        <v>-22.3</v>
       </c>
       <c r="AH3">
-        <v>0.1513342696629214</v>
+        <v>0.05327761817706973</v>
       </c>
       <c r="AI3">
-        <v>0.2734771573604061</v>
+        <v>0.04410810810810811</v>
       </c>
       <c r="AJ3">
-        <v>0.1319806069312264</v>
+        <v>-0.06554967666078779</v>
       </c>
       <c r="AK3">
-        <v>0.2429752066115702</v>
+        <v>-0.05312053358742259</v>
       </c>
       <c r="AL3">
-        <v>0.228</v>
+        <v>0.746</v>
       </c>
       <c r="AM3">
-        <v>0.228</v>
+        <v>0.746</v>
       </c>
       <c r="AN3">
-        <v>-0.4634408602150538</v>
+        <v>0.07464324917672886</v>
       </c>
       <c r="AO3">
-        <v>-885.0877192982456</v>
+        <v>348.5254691689008</v>
       </c>
       <c r="AP3">
-        <v>-0.3951612903225806</v>
+        <v>-0.08159531650201245</v>
       </c>
       <c r="AQ3">
-        <v>-885.0877192982456</v>
+        <v>348.5254691689008</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AS Latvijas Gaze (RISE:GZE1R)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RISE:GZE1R</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0532776181770697</v>
+      </c>
+      <c r="F2">
+        <v>0.99</v>
+      </c>
+      <c r="G2">
+        <v>362.5</v>
+      </c>
+      <c r="H2">
+        <v>11.8178894705661</v>
+      </c>
+      <c r="I2">
+        <v>340.2</v>
+      </c>
+      <c r="J2">
+        <v>348.188889470566</v>
+      </c>
+      <c r="K2">
+        <v>20.4</v>
+      </c>
+      <c r="L2">
+        <v>379.071</v>
+      </c>
+      <c r="M2">
+        <v>0.0746615910699384</v>
+      </c>
+      <c r="N2">
+        <v>0.0651878142243091</v>
+      </c>
+      <c r="O2">
+        <v>0.0495746788990826</v>
+      </c>
+      <c r="P2">
+        <v>0.03656</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.0760733786790017</v>
+      </c>
+      <c r="T2">
+        <v>2.89934142243091</v>
+      </c>
+      <c r="U2">
+        <v>0.466886393300599</v>
+      </c>
+      <c r="V2">
+        <v>35.8311458456038</v>
+      </c>
+      <c r="W2">
+        <v>15.0027032285142</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>362.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.07983393650755573</v>
+      </c>
+      <c r="AC2">
+        <v>0.06196834862385321</v>
+      </c>
+      <c r="AD2">
+        <v>0.2</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>273.3</v>
+      </c>
+      <c r="AH2">
+        <v>13.4</v>
+      </c>
+      <c r="AI2">
+        <v>9.049999999999983</v>
+      </c>
+      <c r="AJ2">
+        <v>20.4</v>
+      </c>
+      <c r="AK2">
+        <v>20.4</v>
+      </c>
+      <c r="AL2">
+        <v>0.746</v>
+      </c>
+      <c r="AM2">
+        <v>20.4</v>
+      </c>
+      <c r="AN2">
+        <v>42.7</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.07446759878342779</v>
+      </c>
+      <c r="C2">
+        <v>383.0599083760986</v>
+      </c>
+      <c r="D2">
+        <v>340.3599083760986</v>
+      </c>
+      <c r="E2">
+        <v>-20.4</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>42.7</v>
+      </c>
+      <c r="H2">
+        <v>362.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>273.3</v>
+      </c>
+      <c r="K2">
+        <v>13.4</v>
+      </c>
+      <c r="L2">
+        <v>259.9</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>259.9</v>
+      </c>
+      <c r="O2">
+        <v>51.98</v>
+      </c>
+      <c r="P2">
+        <v>207.92</v>
+      </c>
+      <c r="Q2">
+        <v>221.3200000000001</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.07446759878342779</v>
+      </c>
+      <c r="T2">
+        <v>0.4467723920898238</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.03656</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.07437386358586093</v>
+      </c>
+      <c r="C3">
+        <v>379.3082284369279</v>
+      </c>
+      <c r="D3">
+        <v>340.437228436928</v>
+      </c>
+      <c r="E3">
+        <v>-16.571</v>
+      </c>
+      <c r="F3">
+        <v>3.829</v>
+      </c>
+      <c r="G3">
+        <v>42.7</v>
+      </c>
+      <c r="H3">
+        <v>362.5</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>273.3</v>
+      </c>
+      <c r="K3">
+        <v>13.4</v>
+      </c>
+      <c r="L3">
+        <v>259.9</v>
+      </c>
+      <c r="M3">
+        <v>0.1749853</v>
+      </c>
+      <c r="N3">
+        <v>259.7250147</v>
+      </c>
+      <c r="O3">
+        <v>51.94500293999999</v>
+      </c>
+      <c r="P3">
+        <v>207.78001176</v>
+      </c>
+      <c r="Q3">
+        <v>221.18001176</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.07475582180389993</v>
+      </c>
+      <c r="T3">
+        <v>0.4503826740461053</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.2</v>
+      </c>
+      <c r="W3">
+        <v>0.03656</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>1485.267619622906</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.07428012838829406</v>
+      </c>
+      <c r="C4">
+        <v>375.5565836355636</v>
+      </c>
+      <c r="D4">
+        <v>340.5145836355636</v>
+      </c>
+      <c r="E4">
+        <v>-12.742</v>
+      </c>
+      <c r="F4">
+        <v>7.657999999999999</v>
+      </c>
+      <c r="G4">
+        <v>42.7</v>
+      </c>
+      <c r="H4">
+        <v>362.5</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>273.3</v>
+      </c>
+      <c r="K4">
+        <v>13.4</v>
+      </c>
+      <c r="L4">
+        <v>259.9</v>
+      </c>
+      <c r="M4">
+        <v>0.3499706</v>
+      </c>
+      <c r="N4">
+        <v>259.5500294</v>
+      </c>
+      <c r="O4">
+        <v>51.91000587999999</v>
+      </c>
+      <c r="P4">
+        <v>207.64002352</v>
+      </c>
+      <c r="Q4">
+        <v>221.04002352</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.07504992692683068</v>
+      </c>
+      <c r="T4">
+        <v>0.4540666352259842</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>0.03656</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>742.6338098114528</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.0741863931907272</v>
+      </c>
+      <c r="C5">
+        <v>371.804973995963</v>
+      </c>
+      <c r="D5">
+        <v>340.591973995963</v>
+      </c>
+      <c r="E5">
+        <v>-8.913</v>
+      </c>
+      <c r="F5">
+        <v>11.487</v>
+      </c>
+      <c r="G5">
+        <v>42.7</v>
+      </c>
+      <c r="H5">
+        <v>362.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>273.3</v>
+      </c>
+      <c r="K5">
+        <v>13.4</v>
+      </c>
+      <c r="L5">
+        <v>259.9</v>
+      </c>
+      <c r="M5">
+        <v>0.5249558999999999</v>
+      </c>
+      <c r="N5">
+        <v>259.3750441</v>
+      </c>
+      <c r="O5">
+        <v>51.87500881999999</v>
+      </c>
+      <c r="P5">
+        <v>207.50003528</v>
+      </c>
+      <c r="Q5">
+        <v>220.90003528</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.07535009607291465</v>
+      </c>
+      <c r="T5">
+        <v>0.4578265543683349</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.2</v>
+      </c>
+      <c r="W5">
+        <v>0.03656</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>495.0892065409686</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.07409265799316037</v>
+      </c>
+      <c r="C6">
+        <v>368.053399542106</v>
+      </c>
+      <c r="D6">
+        <v>340.669399542106</v>
+      </c>
+      <c r="E6">
+        <v>-5.084</v>
+      </c>
+      <c r="F6">
+        <v>15.316</v>
+      </c>
+      <c r="G6">
+        <v>42.7</v>
+      </c>
+      <c r="H6">
+        <v>362.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>273.3</v>
+      </c>
+      <c r="K6">
+        <v>13.4</v>
+      </c>
+      <c r="L6">
+        <v>259.9</v>
+      </c>
+      <c r="M6">
+        <v>0.6999412</v>
+      </c>
+      <c r="N6">
+        <v>259.2000588</v>
+      </c>
+      <c r="O6">
+        <v>51.84001176</v>
+      </c>
+      <c r="P6">
+        <v>207.36004704</v>
+      </c>
+      <c r="Q6">
+        <v>220.76004704</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.07565651874287538</v>
+      </c>
+      <c r="T6">
+        <v>0.4616648051594847</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.2</v>
+      </c>
+      <c r="W6">
+        <v>0.03656</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>371.3169049057264</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.0739989227955935</v>
+      </c>
+      <c r="C7">
+        <v>364.3018602979939</v>
+      </c>
+      <c r="D7">
+        <v>340.7468602979939</v>
+      </c>
+      <c r="E7">
+        <v>-1.254999999999999</v>
+      </c>
+      <c r="F7">
+        <v>19.145</v>
+      </c>
+      <c r="G7">
+        <v>42.7</v>
+      </c>
+      <c r="H7">
+        <v>362.5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>273.3</v>
+      </c>
+      <c r="K7">
+        <v>13.4</v>
+      </c>
+      <c r="L7">
+        <v>259.9</v>
+      </c>
+      <c r="M7">
+        <v>0.8749265000000001</v>
+      </c>
+      <c r="N7">
+        <v>259.0250735</v>
+      </c>
+      <c r="O7">
+        <v>51.80501469999999</v>
+      </c>
+      <c r="P7">
+        <v>207.2200588</v>
+      </c>
+      <c r="Q7">
+        <v>220.6200588</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.07596939241641422</v>
+      </c>
+      <c r="T7">
+        <v>0.4655838612304479</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.03656</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>297.0535239245811</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.07390518759802665</v>
+      </c>
+      <c r="C8">
+        <v>360.5503562876499</v>
+      </c>
+      <c r="D8">
+        <v>340.8243562876499</v>
+      </c>
+      <c r="E8">
+        <v>2.573999999999998</v>
+      </c>
+      <c r="F8">
+        <v>22.974</v>
+      </c>
+      <c r="G8">
+        <v>42.7</v>
+      </c>
+      <c r="H8">
+        <v>362.5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>273.3</v>
+      </c>
+      <c r="K8">
+        <v>13.4</v>
+      </c>
+      <c r="L8">
+        <v>259.9</v>
+      </c>
+      <c r="M8">
+        <v>1.0499118</v>
+      </c>
+      <c r="N8">
+        <v>258.8500882</v>
+      </c>
+      <c r="O8">
+        <v>51.77001763999999</v>
+      </c>
+      <c r="P8">
+        <v>207.08007056</v>
+      </c>
+      <c r="Q8">
+        <v>220.48007056</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.0762889229766241</v>
+      </c>
+      <c r="T8">
+        <v>0.469586301473134</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.03656</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>247.5446032704843</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.0738114524004598</v>
+      </c>
+      <c r="C9">
+        <v>356.7988875351193</v>
+      </c>
+      <c r="D9">
+        <v>340.9018875351193</v>
+      </c>
+      <c r="E9">
+        <v>6.403000000000002</v>
+      </c>
+      <c r="F9">
+        <v>26.803</v>
+      </c>
+      <c r="G9">
+        <v>42.7</v>
+      </c>
+      <c r="H9">
+        <v>362.5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>273.3</v>
+      </c>
+      <c r="K9">
+        <v>13.4</v>
+      </c>
+      <c r="L9">
+        <v>259.9</v>
+      </c>
+      <c r="M9">
+        <v>1.2248971</v>
+      </c>
+      <c r="N9">
+        <v>258.6751029</v>
+      </c>
+      <c r="O9">
+        <v>51.73502057999999</v>
+      </c>
+      <c r="P9">
+        <v>206.94008232</v>
+      </c>
+      <c r="Q9">
+        <v>220.34008232</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.07661532516178474</v>
+      </c>
+      <c r="T9">
+        <v>0.4736748156995337</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.2</v>
+      </c>
+      <c r="W9">
+        <v>0.03656</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>212.1810885175579</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.07371771720289295</v>
+      </c>
+      <c r="C10">
+        <v>353.0474540644688</v>
+      </c>
+      <c r="D10">
+        <v>340.9794540644688</v>
+      </c>
+      <c r="E10">
+        <v>10.232</v>
+      </c>
+      <c r="F10">
+        <v>30.632</v>
+      </c>
+      <c r="G10">
+        <v>42.7</v>
+      </c>
+      <c r="H10">
+        <v>362.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>273.3</v>
+      </c>
+      <c r="K10">
+        <v>13.4</v>
+      </c>
+      <c r="L10">
+        <v>259.9</v>
+      </c>
+      <c r="M10">
+        <v>1.3998824</v>
+      </c>
+      <c r="N10">
+        <v>258.5001176</v>
+      </c>
+      <c r="O10">
+        <v>51.70002351999999</v>
+      </c>
+      <c r="P10">
+        <v>206.80009408</v>
+      </c>
+      <c r="Q10">
+        <v>220.20009408</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.07694882304662276</v>
+      </c>
+      <c r="T10">
+        <v>0.4778522106699855</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10">
+        <v>0.03656</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>185.6584524528632</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.07362398200532609</v>
+      </c>
+      <c r="C11">
+        <v>349.2960558997874</v>
+      </c>
+      <c r="D11">
+        <v>341.0570558997874</v>
+      </c>
+      <c r="E11">
+        <v>14.061</v>
+      </c>
+      <c r="F11">
+        <v>34.461</v>
+      </c>
+      <c r="G11">
+        <v>42.7</v>
+      </c>
+      <c r="H11">
+        <v>362.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>273.3</v>
+      </c>
+      <c r="K11">
+        <v>13.4</v>
+      </c>
+      <c r="L11">
+        <v>259.9</v>
+      </c>
+      <c r="M11">
+        <v>1.5748677</v>
+      </c>
+      <c r="N11">
+        <v>258.3251323</v>
+      </c>
+      <c r="O11">
+        <v>51.66502645999999</v>
+      </c>
+      <c r="P11">
+        <v>206.66010584</v>
+      </c>
+      <c r="Q11">
+        <v>220.06010584</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.0772896505553034</v>
+      </c>
+      <c r="T11">
+        <v>0.4821214165189088</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.2</v>
+      </c>
+      <c r="W11">
+        <v>0.03656</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>165.0297355136562</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.07353024680775924</v>
+      </c>
+      <c r="C12">
+        <v>345.544693065186</v>
+      </c>
+      <c r="D12">
+        <v>341.134693065186</v>
+      </c>
+      <c r="E12">
+        <v>17.89</v>
+      </c>
+      <c r="F12">
+        <v>38.29</v>
+      </c>
+      <c r="G12">
+        <v>42.7</v>
+      </c>
+      <c r="H12">
+        <v>362.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>273.3</v>
+      </c>
+      <c r="K12">
+        <v>13.4</v>
+      </c>
+      <c r="L12">
+        <v>259.9</v>
+      </c>
+      <c r="M12">
+        <v>1.749853</v>
+      </c>
+      <c r="N12">
+        <v>258.1501470000001</v>
+      </c>
+      <c r="O12">
+        <v>51.6300294</v>
+      </c>
+      <c r="P12">
+        <v>206.5201176</v>
+      </c>
+      <c r="Q12">
+        <v>219.9201176000001</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.07763805200862137</v>
+      </c>
+      <c r="T12">
+        <v>0.4864854936089194</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>0.03656</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>148.5267619622906</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.07343651161019236</v>
+      </c>
+      <c r="C13">
+        <v>341.7933655847974</v>
+      </c>
+      <c r="D13">
+        <v>341.2123655847973</v>
+      </c>
+      <c r="E13">
+        <v>21.719</v>
+      </c>
+      <c r="F13">
+        <v>42.119</v>
+      </c>
+      <c r="G13">
+        <v>42.7</v>
+      </c>
+      <c r="H13">
+        <v>362.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>273.3</v>
+      </c>
+      <c r="K13">
+        <v>13.4</v>
+      </c>
+      <c r="L13">
+        <v>259.9</v>
+      </c>
+      <c r="M13">
+        <v>1.9248383</v>
+      </c>
+      <c r="N13">
+        <v>257.9751617000001</v>
+      </c>
+      <c r="O13">
+        <v>51.59503234</v>
+      </c>
+      <c r="P13">
+        <v>206.3801293600001</v>
+      </c>
+      <c r="Q13">
+        <v>219.7801293600001</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.07799428270808131</v>
+      </c>
+      <c r="T13">
+        <v>0.4909476398470199</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.2</v>
+      </c>
+      <c r="W13">
+        <v>0.03656</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>135.0243290566278</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.07334277641262552</v>
+      </c>
+      <c r="C14">
+        <v>338.0420734827761</v>
+      </c>
+      <c r="D14">
+        <v>341.2900734827761</v>
+      </c>
+      <c r="E14">
+        <v>25.54799999999999</v>
+      </c>
+      <c r="F14">
+        <v>45.94799999999999</v>
+      </c>
+      <c r="G14">
+        <v>42.7</v>
+      </c>
+      <c r="H14">
+        <v>362.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>273.3</v>
+      </c>
+      <c r="K14">
+        <v>13.4</v>
+      </c>
+      <c r="L14">
+        <v>259.9</v>
+      </c>
+      <c r="M14">
+        <v>2.0998236</v>
+      </c>
+      <c r="N14">
+        <v>257.8001764000001</v>
+      </c>
+      <c r="O14">
+        <v>51.56003528</v>
+      </c>
+      <c r="P14">
+        <v>206.2401411200001</v>
+      </c>
+      <c r="Q14">
+        <v>219.6401411200001</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.07835860955980173</v>
+      </c>
+      <c r="T14">
+        <v>0.4955111984996228</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.2</v>
+      </c>
+      <c r="W14">
+        <v>0.03656</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>123.7723016352422</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.07324904121505867</v>
+      </c>
+      <c r="C15">
+        <v>334.2908167832991</v>
+      </c>
+      <c r="D15">
+        <v>341.3678167832991</v>
+      </c>
+      <c r="E15">
+        <v>29.377</v>
+      </c>
+      <c r="F15">
+        <v>49.777</v>
+      </c>
+      <c r="G15">
+        <v>42.7</v>
+      </c>
+      <c r="H15">
+        <v>362.5</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>273.3</v>
+      </c>
+      <c r="K15">
+        <v>13.4</v>
+      </c>
+      <c r="L15">
+        <v>259.9</v>
+      </c>
+      <c r="M15">
+        <v>2.2748089</v>
+      </c>
+      <c r="N15">
+        <v>257.6251911000001</v>
+      </c>
+      <c r="O15">
+        <v>51.52503822</v>
+      </c>
+      <c r="P15">
+        <v>206.1001528800001</v>
+      </c>
+      <c r="Q15">
+        <v>219.5001528800001</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.07873131174144674</v>
+      </c>
+      <c r="T15">
+        <v>0.5001796665465383</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.2</v>
+      </c>
+      <c r="W15">
+        <v>0.03656</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>114.2513553556081</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.0731553060174918</v>
+      </c>
+      <c r="C16">
+        <v>330.5395955105652</v>
+      </c>
+      <c r="D16">
+        <v>341.4455955105652</v>
+      </c>
+      <c r="E16">
+        <v>33.206</v>
+      </c>
+      <c r="F16">
+        <v>53.606</v>
+      </c>
+      <c r="G16">
+        <v>42.7</v>
+      </c>
+      <c r="H16">
+        <v>362.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>273.3</v>
+      </c>
+      <c r="K16">
+        <v>13.4</v>
+      </c>
+      <c r="L16">
+        <v>259.9</v>
+      </c>
+      <c r="M16">
+        <v>2.4497942</v>
+      </c>
+      <c r="N16">
+        <v>257.4502058</v>
+      </c>
+      <c r="O16">
+        <v>51.49004116</v>
+      </c>
+      <c r="P16">
+        <v>205.96016464</v>
+      </c>
+      <c r="Q16">
+        <v>219.3601646400001</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.07911268141568815</v>
+      </c>
+      <c r="T16">
+        <v>0.5049567036178009</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.2</v>
+      </c>
+      <c r="W16">
+        <v>0.03656</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>106.090544258779</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.07306157081992495</v>
+      </c>
+      <c r="C17">
+        <v>326.7884096887952</v>
+      </c>
+      <c r="D17">
+        <v>341.5234096887953</v>
+      </c>
+      <c r="E17">
+        <v>37.035</v>
+      </c>
+      <c r="F17">
+        <v>57.435</v>
+      </c>
+      <c r="G17">
+        <v>42.7</v>
+      </c>
+      <c r="H17">
+        <v>362.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>273.3</v>
+      </c>
+      <c r="K17">
+        <v>13.4</v>
+      </c>
+      <c r="L17">
+        <v>259.9</v>
+      </c>
+      <c r="M17">
+        <v>2.6247795</v>
+      </c>
+      <c r="N17">
+        <v>257.2752205</v>
+      </c>
+      <c r="O17">
+        <v>51.45504409999999</v>
+      </c>
+      <c r="P17">
+        <v>205.8201764</v>
+      </c>
+      <c r="Q17">
+        <v>219.2201764</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.07950302449402935</v>
+      </c>
+      <c r="T17">
+        <v>0.5098461415613283</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.2</v>
+      </c>
+      <c r="W17">
+        <v>0.03656</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>99.01784130819372</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.07296783562235809</v>
+      </c>
+      <c r="C18">
+        <v>323.0372593422321</v>
+      </c>
+      <c r="D18">
+        <v>341.6012593422321</v>
+      </c>
+      <c r="E18">
+        <v>40.864</v>
+      </c>
+      <c r="F18">
+        <v>61.264</v>
+      </c>
+      <c r="G18">
+        <v>42.7</v>
+      </c>
+      <c r="H18">
+        <v>362.5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>273.3</v>
+      </c>
+      <c r="K18">
+        <v>13.4</v>
+      </c>
+      <c r="L18">
+        <v>259.9</v>
+      </c>
+      <c r="M18">
+        <v>2.7997648</v>
+      </c>
+      <c r="N18">
+        <v>257.1002352</v>
+      </c>
+      <c r="O18">
+        <v>51.42004704</v>
+      </c>
+      <c r="P18">
+        <v>205.6801881600001</v>
+      </c>
+      <c r="Q18">
+        <v>219.0801881600001</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.07990266145518821</v>
+      </c>
+      <c r="T18">
+        <v>0.5148519946939875</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.2</v>
+      </c>
+      <c r="W18">
+        <v>0.03656</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>92.8292262264316</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.07287410042479124</v>
+      </c>
+      <c r="C19">
+        <v>319.286144495141</v>
+      </c>
+      <c r="D19">
+        <v>341.679144495141</v>
+      </c>
+      <c r="E19">
+        <v>44.693</v>
+      </c>
+      <c r="F19">
+        <v>65.093</v>
+      </c>
+      <c r="G19">
+        <v>42.7</v>
+      </c>
+      <c r="H19">
+        <v>362.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>273.3</v>
+      </c>
+      <c r="K19">
+        <v>13.4</v>
+      </c>
+      <c r="L19">
+        <v>259.9</v>
+      </c>
+      <c r="M19">
+        <v>2.974750100000001</v>
+      </c>
+      <c r="N19">
+        <v>256.9252499</v>
+      </c>
+      <c r="O19">
+        <v>51.38504998</v>
+      </c>
+      <c r="P19">
+        <v>205.54019992</v>
+      </c>
+      <c r="Q19">
+        <v>218.9401999200001</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.08031192822264005</v>
+      </c>
+      <c r="T19">
+        <v>0.5199784707936985</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.2</v>
+      </c>
+      <c r="W19">
+        <v>0.03656</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>87.36868350722973</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.07278036522722439</v>
+      </c>
+      <c r="C20">
+        <v>315.535065171809</v>
+      </c>
+      <c r="D20">
+        <v>341.7570651718091</v>
+      </c>
+      <c r="E20">
+        <v>48.522</v>
+      </c>
+      <c r="F20">
+        <v>68.922</v>
+      </c>
+      <c r="G20">
+        <v>42.7</v>
+      </c>
+      <c r="H20">
+        <v>362.5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>273.3</v>
+      </c>
+      <c r="K20">
+        <v>13.4</v>
+      </c>
+      <c r="L20">
+        <v>259.9</v>
+      </c>
+      <c r="M20">
+        <v>3.1497354</v>
+      </c>
+      <c r="N20">
+        <v>256.7502646</v>
+      </c>
+      <c r="O20">
+        <v>51.35005292</v>
+      </c>
+      <c r="P20">
+        <v>205.40021168</v>
+      </c>
+      <c r="Q20">
+        <v>218.80021168</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.0807311771063712</v>
+      </c>
+      <c r="T20">
+        <v>0.5252299828958417</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.2</v>
+      </c>
+      <c r="W20">
+        <v>0.03656</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>82.5148677568281</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.07268663002965754</v>
+      </c>
+      <c r="C21">
+        <v>311.7840213965455</v>
+      </c>
+      <c r="D21">
+        <v>341.8350213965455</v>
+      </c>
+      <c r="E21">
+        <v>52.35099999999999</v>
+      </c>
+      <c r="F21">
+        <v>72.75099999999999</v>
+      </c>
+      <c r="G21">
+        <v>42.7</v>
+      </c>
+      <c r="H21">
+        <v>362.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>273.3</v>
+      </c>
+      <c r="K21">
+        <v>13.4</v>
+      </c>
+      <c r="L21">
+        <v>259.9</v>
+      </c>
+      <c r="M21">
+        <v>3.3247207</v>
+      </c>
+      <c r="N21">
+        <v>256.5752793</v>
+      </c>
+      <c r="O21">
+        <v>51.31505585999999</v>
+      </c>
+      <c r="P21">
+        <v>205.26022344</v>
+      </c>
+      <c r="Q21">
+        <v>218.66022344</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.08116077781439202</v>
+      </c>
+      <c r="T21">
+        <v>0.5306111619634698</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.2</v>
+      </c>
+      <c r="W21">
+        <v>0.03656</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>78.17197998015293</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.07259289483209068</v>
+      </c>
+      <c r="C22">
+        <v>308.0330131936821</v>
+      </c>
+      <c r="D22">
+        <v>341.9130131936821</v>
+      </c>
+      <c r="E22">
+        <v>56.18</v>
+      </c>
+      <c r="F22">
+        <v>76.58</v>
+      </c>
+      <c r="G22">
+        <v>42.7</v>
+      </c>
+      <c r="H22">
+        <v>362.5</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>273.3</v>
+      </c>
+      <c r="K22">
+        <v>13.4</v>
+      </c>
+      <c r="L22">
+        <v>259.9</v>
+      </c>
+      <c r="M22">
+        <v>3.499706</v>
+      </c>
+      <c r="N22">
+        <v>256.400294</v>
+      </c>
+      <c r="O22">
+        <v>51.28005879999999</v>
+      </c>
+      <c r="P22">
+        <v>205.1202352</v>
+      </c>
+      <c r="Q22">
+        <v>218.5202352</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.08160111854011334</v>
+      </c>
+      <c r="T22">
+        <v>0.5361268705077886</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.2</v>
+      </c>
+      <c r="W22">
+        <v>0.03656</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>74.26338098114527</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.07249915963452383</v>
+      </c>
+      <c r="C23">
+        <v>304.2820405875725</v>
+      </c>
+      <c r="D23">
+        <v>341.9910405875725</v>
+      </c>
+      <c r="E23">
+        <v>60.00899999999999</v>
+      </c>
+      <c r="F23">
+        <v>80.40899999999999</v>
+      </c>
+      <c r="G23">
+        <v>42.7</v>
+      </c>
+      <c r="H23">
+        <v>362.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>273.3</v>
+      </c>
+      <c r="K23">
+        <v>13.4</v>
+      </c>
+      <c r="L23">
+        <v>259.9</v>
+      </c>
+      <c r="M23">
+        <v>3.6746913</v>
+      </c>
+      <c r="N23">
+        <v>256.2253087</v>
+      </c>
+      <c r="O23">
+        <v>51.24506174</v>
+      </c>
+      <c r="P23">
+        <v>204.98024696</v>
+      </c>
+      <c r="Q23">
+        <v>218.3802469600001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.08205260713230864</v>
+      </c>
+      <c r="T23">
+        <v>0.5417822172431028</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.2</v>
+      </c>
+      <c r="W23">
+        <v>0.03656</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>70.72702950585264</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.07240542443695697</v>
+      </c>
+      <c r="C24">
+        <v>300.5311036025926</v>
+      </c>
+      <c r="D24">
+        <v>342.0691036025926</v>
+      </c>
+      <c r="E24">
+        <v>63.838</v>
+      </c>
+      <c r="F24">
+        <v>84.238</v>
+      </c>
+      <c r="G24">
+        <v>42.7</v>
+      </c>
+      <c r="H24">
+        <v>362.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>273.3</v>
+      </c>
+      <c r="K24">
+        <v>13.4</v>
+      </c>
+      <c r="L24">
+        <v>259.9</v>
+      </c>
+      <c r="M24">
+        <v>3.8496766</v>
+      </c>
+      <c r="N24">
+        <v>256.0503234</v>
+      </c>
+      <c r="O24">
+        <v>51.21006468</v>
+      </c>
+      <c r="P24">
+        <v>204.84025872</v>
+      </c>
+      <c r="Q24">
+        <v>218.24025872</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.08251567235507304</v>
+      </c>
+      <c r="T24">
+        <v>0.5475825728690662</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.2</v>
+      </c>
+      <c r="W24">
+        <v>0.03656</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>67.51216452831389</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.07231168923939013</v>
+      </c>
+      <c r="C25">
+        <v>296.7802022631408</v>
+      </c>
+      <c r="D25">
+        <v>342.1472022631408</v>
+      </c>
+      <c r="E25">
+        <v>67.667</v>
+      </c>
+      <c r="F25">
+        <v>88.06699999999999</v>
+      </c>
+      <c r="G25">
+        <v>42.7</v>
+      </c>
+      <c r="H25">
+        <v>362.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>273.3</v>
+      </c>
+      <c r="K25">
+        <v>13.4</v>
+      </c>
+      <c r="L25">
+        <v>259.9</v>
+      </c>
+      <c r="M25">
+        <v>4.0246619</v>
+      </c>
+      <c r="N25">
+        <v>255.8753381</v>
+      </c>
+      <c r="O25">
+        <v>51.17506761999999</v>
+      </c>
+      <c r="P25">
+        <v>204.70027048</v>
+      </c>
+      <c r="Q25">
+        <v>218.10027048</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.08299076524596119</v>
+      </c>
+      <c r="T25">
+        <v>0.5535335870827168</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.2</v>
+      </c>
+      <c r="W25">
+        <v>0.03656</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>64.57685302708285</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.07221795404182325</v>
+      </c>
+      <c r="C26">
+        <v>293.0293365936376</v>
+      </c>
+      <c r="D26">
+        <v>342.2253365936376</v>
+      </c>
+      <c r="E26">
+        <v>71.49599999999998</v>
+      </c>
+      <c r="F26">
+        <v>91.89599999999999</v>
+      </c>
+      <c r="G26">
+        <v>42.7</v>
+      </c>
+      <c r="H26">
+        <v>362.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>273.3</v>
+      </c>
+      <c r="K26">
+        <v>13.4</v>
+      </c>
+      <c r="L26">
+        <v>259.9</v>
+      </c>
+      <c r="M26">
+        <v>4.199647199999999</v>
+      </c>
+      <c r="N26">
+        <v>255.7003528</v>
+      </c>
+      <c r="O26">
+        <v>51.14007056</v>
+      </c>
+      <c r="P26">
+        <v>204.56028224</v>
+      </c>
+      <c r="Q26">
+        <v>217.9602822400001</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.08347836058134639</v>
+      </c>
+      <c r="T26">
+        <v>0.5596412069335688</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.2</v>
+      </c>
+      <c r="W26">
+        <v>0.03656</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>61.88615081762108</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.07212421884425639</v>
+      </c>
+      <c r="C27">
+        <v>289.2785066185257</v>
+      </c>
+      <c r="D27">
+        <v>342.3035066185258</v>
+      </c>
+      <c r="E27">
+        <v>75.32499999999999</v>
+      </c>
+      <c r="F27">
+        <v>95.72499999999999</v>
+      </c>
+      <c r="G27">
+        <v>42.7</v>
+      </c>
+      <c r="H27">
+        <v>362.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>273.3</v>
+      </c>
+      <c r="K27">
+        <v>13.4</v>
+      </c>
+      <c r="L27">
+        <v>259.9</v>
+      </c>
+      <c r="M27">
+        <v>4.374632500000001</v>
+      </c>
+      <c r="N27">
+        <v>255.5253675</v>
+      </c>
+      <c r="O27">
+        <v>51.1050735</v>
+      </c>
+      <c r="P27">
+        <v>204.420294</v>
+      </c>
+      <c r="Q27">
+        <v>217.820294</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.08397895845900853</v>
+      </c>
+      <c r="T27">
+        <v>0.5659116966471102</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0.2</v>
+      </c>
+      <c r="W27">
+        <v>0.03656</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>59.41070478491622</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.07203048364668956</v>
+      </c>
+      <c r="C28">
+        <v>285.5277123622706</v>
+      </c>
+      <c r="D28">
+        <v>342.3817123622705</v>
+      </c>
+      <c r="E28">
+        <v>79.154</v>
+      </c>
+      <c r="F28">
+        <v>99.554</v>
+      </c>
+      <c r="G28">
+        <v>42.7</v>
+      </c>
+      <c r="H28">
+        <v>362.5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>273.3</v>
+      </c>
+      <c r="K28">
+        <v>13.4</v>
+      </c>
+      <c r="L28">
+        <v>259.9</v>
+      </c>
+      <c r="M28">
+        <v>4.549617800000001</v>
+      </c>
+      <c r="N28">
+        <v>255.3503822</v>
+      </c>
+      <c r="O28">
+        <v>51.07007643999999</v>
+      </c>
+      <c r="P28">
+        <v>204.28030576</v>
+      </c>
+      <c r="Q28">
+        <v>217.68030576</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.08449308600903993</v>
+      </c>
+      <c r="T28">
+        <v>0.5723516590556121</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0.2</v>
+      </c>
+      <c r="W28">
+        <v>0.03656</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>57.12567767780406</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.07193674844912269</v>
+      </c>
+      <c r="C29">
+        <v>281.7769538493595</v>
+      </c>
+      <c r="D29">
+        <v>342.4599538493595</v>
+      </c>
+      <c r="E29">
+        <v>82.983</v>
+      </c>
+      <c r="F29">
+        <v>103.383</v>
+      </c>
+      <c r="G29">
+        <v>42.7</v>
+      </c>
+      <c r="H29">
+        <v>362.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>273.3</v>
+      </c>
+      <c r="K29">
+        <v>13.4</v>
+      </c>
+      <c r="L29">
+        <v>259.9</v>
+      </c>
+      <c r="M29">
+        <v>4.7246031</v>
+      </c>
+      <c r="N29">
+        <v>255.1753969</v>
+      </c>
+      <c r="O29">
+        <v>51.03507938</v>
+      </c>
+      <c r="P29">
+        <v>204.1403175200001</v>
+      </c>
+      <c r="Q29">
+        <v>217.5403175200001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.08502129924537355</v>
+      </c>
+      <c r="T29">
+        <v>0.5789680587903745</v>
+      </c>
+      <c r="U29">
+        <v>0.0457</v>
+      </c>
+      <c r="V29">
+        <v>0.2</v>
+      </c>
+      <c r="W29">
+        <v>0.03656</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>55.00991183788539</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.07184301325155583</v>
+      </c>
+      <c r="C30">
+        <v>278.0262311043025</v>
+      </c>
+      <c r="D30">
+        <v>342.5382311043025</v>
+      </c>
+      <c r="E30">
+        <v>86.81200000000001</v>
+      </c>
+      <c r="F30">
+        <v>107.212</v>
+      </c>
+      <c r="G30">
+        <v>42.7</v>
+      </c>
+      <c r="H30">
+        <v>362.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>273.3</v>
+      </c>
+      <c r="K30">
+        <v>13.4</v>
+      </c>
+      <c r="L30">
+        <v>259.9</v>
+      </c>
+      <c r="M30">
+        <v>4.899588400000001</v>
+      </c>
+      <c r="N30">
+        <v>255.0004116</v>
+      </c>
+      <c r="O30">
+        <v>51.00008232</v>
+      </c>
+      <c r="P30">
+        <v>204.00032928</v>
+      </c>
+      <c r="Q30">
+        <v>217.4003292800001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.08556418507160532</v>
+      </c>
+      <c r="T30">
+        <v>0.5857682474066579</v>
+      </c>
+      <c r="U30">
+        <v>0.0457</v>
+      </c>
+      <c r="V30">
+        <v>0.2</v>
+      </c>
+      <c r="W30">
+        <v>0.03656</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>53.04527212938948</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.07174927805398898</v>
+      </c>
+      <c r="C31">
+        <v>274.2755441516321</v>
+      </c>
+      <c r="D31">
+        <v>342.6165441516321</v>
+      </c>
+      <c r="E31">
+        <v>90.64099999999999</v>
+      </c>
+      <c r="F31">
+        <v>111.041</v>
+      </c>
+      <c r="G31">
+        <v>42.7</v>
+      </c>
+      <c r="H31">
+        <v>362.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>273.3</v>
+      </c>
+      <c r="K31">
+        <v>13.4</v>
+      </c>
+      <c r="L31">
+        <v>259.9</v>
+      </c>
+      <c r="M31">
+        <v>5.074573699999999</v>
+      </c>
+      <c r="N31">
+        <v>254.8254263</v>
+      </c>
+      <c r="O31">
+        <v>50.96508526</v>
+      </c>
+      <c r="P31">
+        <v>203.86034104</v>
+      </c>
+      <c r="Q31">
+        <v>217.26034104</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.08612236345632251</v>
+      </c>
+      <c r="T31">
+        <v>0.5927599906318508</v>
+      </c>
+      <c r="U31">
+        <v>0.0457</v>
+      </c>
+      <c r="V31">
+        <v>0.2</v>
+      </c>
+      <c r="W31">
+        <v>0.03656</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>51.21612481458296</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.07165554285642213</v>
+      </c>
+      <c r="C32">
+        <v>270.5248930159028</v>
+      </c>
+      <c r="D32">
+        <v>342.6948930159028</v>
+      </c>
+      <c r="E32">
+        <v>94.47</v>
+      </c>
+      <c r="F32">
+        <v>114.87</v>
+      </c>
+      <c r="G32">
+        <v>42.7</v>
+      </c>
+      <c r="H32">
+        <v>362.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>273.3</v>
+      </c>
+      <c r="K32">
+        <v>13.4</v>
+      </c>
+      <c r="L32">
+        <v>259.9</v>
+      </c>
+      <c r="M32">
+        <v>5.249559</v>
+      </c>
+      <c r="N32">
+        <v>254.650441</v>
+      </c>
+      <c r="O32">
+        <v>50.93008819999999</v>
+      </c>
+      <c r="P32">
+        <v>203.7203528</v>
+      </c>
+      <c r="Q32">
+        <v>217.1203528</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.08669648979488875</v>
+      </c>
+      <c r="T32">
+        <v>0.599951497949192</v>
+      </c>
+      <c r="U32">
+        <v>0.0457</v>
+      </c>
+      <c r="V32">
+        <v>0.2</v>
+      </c>
+      <c r="W32">
+        <v>0.03656</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>49.50892065409685</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.07156180765885527</v>
+      </c>
+      <c r="C33">
+        <v>266.774277721692</v>
+      </c>
+      <c r="D33">
+        <v>342.773277721692</v>
+      </c>
+      <c r="E33">
+        <v>98.29900000000001</v>
+      </c>
+      <c r="F33">
+        <v>118.699</v>
+      </c>
+      <c r="G33">
+        <v>42.7</v>
+      </c>
+      <c r="H33">
+        <v>362.5</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>273.3</v>
+      </c>
+      <c r="K33">
+        <v>13.4</v>
+      </c>
+      <c r="L33">
+        <v>259.9</v>
+      </c>
+      <c r="M33">
+        <v>5.424544300000001</v>
+      </c>
+      <c r="N33">
+        <v>254.4754557</v>
+      </c>
+      <c r="O33">
+        <v>50.89509113999999</v>
+      </c>
+      <c r="P33">
+        <v>203.58036456</v>
+      </c>
+      <c r="Q33">
+        <v>216.98036456</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.08728725747660185</v>
+      </c>
+      <c r="T33">
+        <v>0.6073514547539924</v>
+      </c>
+      <c r="U33">
+        <v>0.0457</v>
+      </c>
+      <c r="V33">
+        <v>0.2</v>
+      </c>
+      <c r="W33">
+        <v>0.03656</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>47.91185869751308</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.0714680724612884</v>
+      </c>
+      <c r="C34">
+        <v>263.0236982935995</v>
+      </c>
+      <c r="D34">
+        <v>342.8516982935996</v>
+      </c>
+      <c r="E34">
+        <v>102.128</v>
+      </c>
+      <c r="F34">
+        <v>122.528</v>
+      </c>
+      <c r="G34">
+        <v>42.7</v>
+      </c>
+      <c r="H34">
+        <v>362.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>273.3</v>
+      </c>
+      <c r="K34">
+        <v>13.4</v>
+      </c>
+      <c r="L34">
+        <v>259.9</v>
+      </c>
+      <c r="M34">
+        <v>5.5995296</v>
+      </c>
+      <c r="N34">
+        <v>254.3004704</v>
+      </c>
+      <c r="O34">
+        <v>50.86009408</v>
+      </c>
+      <c r="P34">
+        <v>203.44037632</v>
+      </c>
+      <c r="Q34">
+        <v>216.84037632</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.08789540067836531</v>
+      </c>
+      <c r="T34">
+        <v>0.6149690573471692</v>
+      </c>
+      <c r="U34">
+        <v>0.0457</v>
+      </c>
+      <c r="V34">
+        <v>0.2</v>
+      </c>
+      <c r="W34">
+        <v>0.03656</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>46.4146131132158</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.07137433726372155</v>
+      </c>
+      <c r="C35">
+        <v>259.2731547562475</v>
+      </c>
+      <c r="D35">
+        <v>342.9301547562476</v>
+      </c>
+      <c r="E35">
+        <v>105.957</v>
+      </c>
+      <c r="F35">
+        <v>126.357</v>
+      </c>
+      <c r="G35">
+        <v>42.7</v>
+      </c>
+      <c r="H35">
+        <v>362.5</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>273.3</v>
+      </c>
+      <c r="K35">
+        <v>13.4</v>
+      </c>
+      <c r="L35">
+        <v>259.9</v>
+      </c>
+      <c r="M35">
+        <v>5.774514900000001</v>
+      </c>
+      <c r="N35">
+        <v>254.1254851</v>
+      </c>
+      <c r="O35">
+        <v>50.82509701999999</v>
+      </c>
+      <c r="P35">
+        <v>203.30038808</v>
+      </c>
+      <c r="Q35">
+        <v>216.70038808</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.08852169740853963</v>
+      </c>
+      <c r="T35">
+        <v>0.6228140510625305</v>
+      </c>
+      <c r="U35">
+        <v>0.0457</v>
+      </c>
+      <c r="V35">
+        <v>0.2</v>
+      </c>
+      <c r="W35">
+        <v>0.03656</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>45.00810968554259</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.07128060206615469</v>
+      </c>
+      <c r="C36">
+        <v>255.522647134281</v>
+      </c>
+      <c r="D36">
+        <v>343.008647134281</v>
+      </c>
+      <c r="E36">
+        <v>109.786</v>
+      </c>
+      <c r="F36">
+        <v>130.186</v>
+      </c>
+      <c r="G36">
+        <v>42.7</v>
+      </c>
+      <c r="H36">
+        <v>362.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>273.3</v>
+      </c>
+      <c r="K36">
+        <v>13.4</v>
+      </c>
+      <c r="L36">
+        <v>259.9</v>
+      </c>
+      <c r="M36">
+        <v>5.949500200000001</v>
+      </c>
+      <c r="N36">
+        <v>253.9504998</v>
+      </c>
+      <c r="O36">
+        <v>50.79009996</v>
+      </c>
+      <c r="P36">
+        <v>203.1603998400001</v>
+      </c>
+      <c r="Q36">
+        <v>216.5603998400001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.08916697282750713</v>
+      </c>
+      <c r="T36">
+        <v>0.6308967718601755</v>
+      </c>
+      <c r="U36">
+        <v>0.0457</v>
+      </c>
+      <c r="V36">
+        <v>0.2</v>
+      </c>
+      <c r="W36">
+        <v>0.03656</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>43.68434175361487</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.07118686686858784</v>
+      </c>
+      <c r="C37">
+        <v>251.772175452367</v>
+      </c>
+      <c r="D37">
+        <v>343.087175452367</v>
+      </c>
+      <c r="E37">
+        <v>113.615</v>
+      </c>
+      <c r="F37">
+        <v>134.015</v>
+      </c>
+      <c r="G37">
+        <v>42.7</v>
+      </c>
+      <c r="H37">
+        <v>362.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>273.3</v>
+      </c>
+      <c r="K37">
+        <v>13.4</v>
+      </c>
+      <c r="L37">
+        <v>259.9</v>
+      </c>
+      <c r="M37">
+        <v>6.124485500000001</v>
+      </c>
+      <c r="N37">
+        <v>253.7755145</v>
+      </c>
+      <c r="O37">
+        <v>50.7551029</v>
+      </c>
+      <c r="P37">
+        <v>203.0204116</v>
+      </c>
+      <c r="Q37">
+        <v>216.4204116000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.08983210287475053</v>
+      </c>
+      <c r="T37">
+        <v>0.6392281917592865</v>
+      </c>
+      <c r="U37">
+        <v>0.0457</v>
+      </c>
+      <c r="V37">
+        <v>0.2</v>
+      </c>
+      <c r="W37">
+        <v>0.03656</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>42.43621770351158</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.07109313167102099</v>
+      </c>
+      <c r="C38">
+        <v>248.0217397351958</v>
+      </c>
+      <c r="D38">
+        <v>343.1657397351958</v>
+      </c>
+      <c r="E38">
+        <v>117.444</v>
+      </c>
+      <c r="F38">
+        <v>137.844</v>
+      </c>
+      <c r="G38">
+        <v>42.7</v>
+      </c>
+      <c r="H38">
+        <v>362.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>273.3</v>
+      </c>
+      <c r="K38">
+        <v>13.4</v>
+      </c>
+      <c r="L38">
+        <v>259.9</v>
+      </c>
+      <c r="M38">
+        <v>6.2994708</v>
+      </c>
+      <c r="N38">
+        <v>253.6005292</v>
+      </c>
+      <c r="O38">
+        <v>50.72010584</v>
+      </c>
+      <c r="P38">
+        <v>202.88042336</v>
+      </c>
+      <c r="Q38">
+        <v>216.28042336</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.09051801823597029</v>
+      </c>
+      <c r="T38">
+        <v>0.6478199685302445</v>
+      </c>
+      <c r="U38">
+        <v>0.0457</v>
+      </c>
+      <c r="V38">
+        <v>0.2</v>
+      </c>
+      <c r="W38">
+        <v>0.03656</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>41.25743387841405</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.07099939647345413</v>
+      </c>
+      <c r="C39">
+        <v>244.2713400074799</v>
+      </c>
+      <c r="D39">
+        <v>343.2443400074799</v>
+      </c>
+      <c r="E39">
+        <v>121.273</v>
+      </c>
+      <c r="F39">
+        <v>141.673</v>
+      </c>
+      <c r="G39">
+        <v>42.7</v>
+      </c>
+      <c r="H39">
+        <v>362.5</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>273.3</v>
+      </c>
+      <c r="K39">
+        <v>13.4</v>
+      </c>
+      <c r="L39">
+        <v>259.9</v>
+      </c>
+      <c r="M39">
+        <v>6.474456100000001</v>
+      </c>
+      <c r="N39">
+        <v>253.4255439</v>
+      </c>
+      <c r="O39">
+        <v>50.68510877999999</v>
+      </c>
+      <c r="P39">
+        <v>202.74043512</v>
+      </c>
+      <c r="Q39">
+        <v>216.14043512</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.09122570868802243</v>
+      </c>
+      <c r="T39">
+        <v>0.6566845001193284</v>
+      </c>
+      <c r="U39">
+        <v>0.0457</v>
+      </c>
+      <c r="V39">
+        <v>0.2</v>
+      </c>
+      <c r="W39">
+        <v>0.03656</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>40.14236809791636</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.07090566127588728</v>
+      </c>
+      <c r="C40">
+        <v>240.5209762939544</v>
+      </c>
+      <c r="D40">
+        <v>343.3229762939544</v>
+      </c>
+      <c r="E40">
+        <v>125.102</v>
+      </c>
+      <c r="F40">
+        <v>145.502</v>
+      </c>
+      <c r="G40">
+        <v>42.7</v>
+      </c>
+      <c r="H40">
+        <v>362.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>273.3</v>
+      </c>
+      <c r="K40">
+        <v>13.4</v>
+      </c>
+      <c r="L40">
+        <v>259.9</v>
+      </c>
+      <c r="M40">
+        <v>6.6494414</v>
+      </c>
+      <c r="N40">
+        <v>253.2505586</v>
+      </c>
+      <c r="O40">
+        <v>50.65011172</v>
+      </c>
+      <c r="P40">
+        <v>202.60044688</v>
+      </c>
+      <c r="Q40">
+        <v>216.0004468800001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.09195622786433431</v>
+      </c>
+      <c r="T40">
+        <v>0.6658349843403181</v>
+      </c>
+      <c r="U40">
+        <v>0.0457</v>
+      </c>
+      <c r="V40">
+        <v>0.2</v>
+      </c>
+      <c r="W40">
+        <v>0.03656</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>39.08598999007646</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.07081192607832042</v>
+      </c>
+      <c r="C41">
+        <v>236.7706486193774</v>
+      </c>
+      <c r="D41">
+        <v>343.4016486193774</v>
+      </c>
+      <c r="E41">
+        <v>128.931</v>
+      </c>
+      <c r="F41">
+        <v>149.331</v>
+      </c>
+      <c r="G41">
+        <v>42.7</v>
+      </c>
+      <c r="H41">
+        <v>362.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>273.3</v>
+      </c>
+      <c r="K41">
+        <v>13.4</v>
+      </c>
+      <c r="L41">
+        <v>259.9</v>
+      </c>
+      <c r="M41">
+        <v>6.8244267</v>
+      </c>
+      <c r="N41">
+        <v>253.0755733</v>
+      </c>
+      <c r="O41">
+        <v>50.61511466</v>
+      </c>
+      <c r="P41">
+        <v>202.46045864</v>
+      </c>
+      <c r="Q41">
+        <v>215.86045864</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.09271069848904986</v>
+      </c>
+      <c r="T41">
+        <v>0.6752854844374059</v>
+      </c>
+      <c r="U41">
+        <v>0.0457</v>
+      </c>
+      <c r="V41">
+        <v>0.2</v>
+      </c>
+      <c r="W41">
+        <v>0.03656</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>38.08378511853604</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.07071819088075357</v>
+      </c>
+      <c r="C42">
+        <v>233.0203570085295</v>
+      </c>
+      <c r="D42">
+        <v>343.4803570085295</v>
+      </c>
+      <c r="E42">
+        <v>132.76</v>
+      </c>
+      <c r="F42">
+        <v>153.16</v>
+      </c>
+      <c r="G42">
+        <v>42.7</v>
+      </c>
+      <c r="H42">
+        <v>362.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>273.3</v>
+      </c>
+      <c r="K42">
+        <v>13.4</v>
+      </c>
+      <c r="L42">
+        <v>259.9</v>
+      </c>
+      <c r="M42">
+        <v>6.999412</v>
+      </c>
+      <c r="N42">
+        <v>252.900588</v>
+      </c>
+      <c r="O42">
+        <v>50.58011759999999</v>
+      </c>
+      <c r="P42">
+        <v>202.3204704</v>
+      </c>
+      <c r="Q42">
+        <v>215.7204704</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.09349031813458927</v>
+      </c>
+      <c r="T42">
+        <v>0.6850510012043965</v>
+      </c>
+      <c r="U42">
+        <v>0.0457</v>
+      </c>
+      <c r="V42">
+        <v>0.2</v>
+      </c>
+      <c r="W42">
+        <v>0.03656</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>37.13169049057264</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.0706244556831867</v>
+      </c>
+      <c r="C43">
+        <v>229.2701014862139</v>
+      </c>
+      <c r="D43">
+        <v>343.5591014862139</v>
+      </c>
+      <c r="E43">
+        <v>136.589</v>
+      </c>
+      <c r="F43">
+        <v>156.989</v>
+      </c>
+      <c r="G43">
+        <v>42.7</v>
+      </c>
+      <c r="H43">
+        <v>362.5</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>273.3</v>
+      </c>
+      <c r="K43">
+        <v>13.4</v>
+      </c>
+      <c r="L43">
+        <v>259.9</v>
+      </c>
+      <c r="M43">
+        <v>7.174397300000001</v>
+      </c>
+      <c r="N43">
+        <v>252.7256027</v>
+      </c>
+      <c r="O43">
+        <v>50.54512053999999</v>
+      </c>
+      <c r="P43">
+        <v>202.18048216</v>
+      </c>
+      <c r="Q43">
+        <v>215.58048216</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.09429636556472323</v>
+      </c>
+      <c r="T43">
+        <v>0.6951475524380649</v>
+      </c>
+      <c r="U43">
+        <v>0.0457</v>
+      </c>
+      <c r="V43">
+        <v>0.2</v>
+      </c>
+      <c r="W43">
+        <v>0.03656</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>36.22603950299769</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.07053072048561985</v>
+      </c>
+      <c r="C44">
+        <v>225.5198820772567</v>
+      </c>
+      <c r="D44">
+        <v>343.6378820772567</v>
+      </c>
+      <c r="E44">
+        <v>140.418</v>
+      </c>
+      <c r="F44">
+        <v>160.818</v>
+      </c>
+      <c r="G44">
+        <v>42.7</v>
+      </c>
+      <c r="H44">
+        <v>362.5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>273.3</v>
+      </c>
+      <c r="K44">
+        <v>13.4</v>
+      </c>
+      <c r="L44">
+        <v>259.9</v>
+      </c>
+      <c r="M44">
+        <v>7.3493826</v>
+      </c>
+      <c r="N44">
+        <v>252.5506174</v>
+      </c>
+      <c r="O44">
+        <v>50.51012347999999</v>
+      </c>
+      <c r="P44">
+        <v>202.04049392</v>
+      </c>
+      <c r="Q44">
+        <v>215.44049392</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.09513020773382733</v>
+      </c>
+      <c r="T44">
+        <v>0.7055922606108251</v>
+      </c>
+      <c r="U44">
+        <v>0.0457</v>
+      </c>
+      <c r="V44">
+        <v>0.2</v>
+      </c>
+      <c r="W44">
+        <v>0.03656</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>35.36351475292632</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.07043698528805301</v>
+      </c>
+      <c r="C45">
+        <v>221.769698806507</v>
+      </c>
+      <c r="D45">
+        <v>343.716698806507</v>
+      </c>
+      <c r="E45">
+        <v>144.247</v>
+      </c>
+      <c r="F45">
+        <v>164.647</v>
+      </c>
+      <c r="G45">
+        <v>42.7</v>
+      </c>
+      <c r="H45">
+        <v>362.5</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>273.3</v>
+      </c>
+      <c r="K45">
+        <v>13.4</v>
+      </c>
+      <c r="L45">
+        <v>259.9</v>
+      </c>
+      <c r="M45">
+        <v>7.524367900000001</v>
+      </c>
+      <c r="N45">
+        <v>252.3756321</v>
+      </c>
+      <c r="O45">
+        <v>50.47512642</v>
+      </c>
+      <c r="P45">
+        <v>201.90050568</v>
+      </c>
+      <c r="Q45">
+        <v>215.30050568</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.0959933075229</v>
+      </c>
+      <c r="T45">
+        <v>0.7164034497721036</v>
+      </c>
+      <c r="U45">
+        <v>0.0457</v>
+      </c>
+      <c r="V45">
+        <v>0.2</v>
+      </c>
+      <c r="W45">
+        <v>0.03656</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>34.54110743309083</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.07034325009048614</v>
+      </c>
+      <c r="C46">
+        <v>218.0195516988362</v>
+      </c>
+      <c r="D46">
+        <v>343.7955516988362</v>
+      </c>
+      <c r="E46">
+        <v>148.076</v>
+      </c>
+      <c r="F46">
+        <v>168.476</v>
+      </c>
+      <c r="G46">
+        <v>42.7</v>
+      </c>
+      <c r="H46">
+        <v>362.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>273.3</v>
+      </c>
+      <c r="K46">
+        <v>13.4</v>
+      </c>
+      <c r="L46">
+        <v>259.9</v>
+      </c>
+      <c r="M46">
+        <v>7.699353200000001</v>
+      </c>
+      <c r="N46">
+        <v>252.2006468</v>
+      </c>
+      <c r="O46">
+        <v>50.44012936</v>
+      </c>
+      <c r="P46">
+        <v>201.7605174400001</v>
+      </c>
+      <c r="Q46">
+        <v>215.1605174400001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.09688723230443955</v>
+      </c>
+      <c r="T46">
+        <v>0.7276007528319988</v>
+      </c>
+      <c r="U46">
+        <v>0.0457</v>
+      </c>
+      <c r="V46">
+        <v>0.2</v>
+      </c>
+      <c r="W46">
+        <v>0.03656</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>33.75608226415694</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.07024951489291931</v>
+      </c>
+      <c r="C47">
+        <v>214.2694407791389</v>
+      </c>
+      <c r="D47">
+        <v>343.8744407791389</v>
+      </c>
+      <c r="E47">
+        <v>151.905</v>
+      </c>
+      <c r="F47">
+        <v>172.305</v>
+      </c>
+      <c r="G47">
+        <v>42.7</v>
+      </c>
+      <c r="H47">
+        <v>362.5</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>273.3</v>
+      </c>
+      <c r="K47">
+        <v>13.4</v>
+      </c>
+      <c r="L47">
+        <v>259.9</v>
+      </c>
+      <c r="M47">
+        <v>7.874338500000001</v>
+      </c>
+      <c r="N47">
+        <v>252.0256615</v>
+      </c>
+      <c r="O47">
+        <v>50.4051323</v>
+      </c>
+      <c r="P47">
+        <v>201.6205292</v>
+      </c>
+      <c r="Q47">
+        <v>215.0205292000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.09781366344167144</v>
+      </c>
+      <c r="T47">
+        <v>0.7392052305486176</v>
+      </c>
+      <c r="U47">
+        <v>0.0457</v>
+      </c>
+      <c r="V47">
+        <v>0.2</v>
+      </c>
+      <c r="W47">
+        <v>0.03656</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>33.00594710273123</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.07015577969535244</v>
+      </c>
+      <c r="C48">
+        <v>210.5193660723325</v>
+      </c>
+      <c r="D48">
+        <v>343.9533660723325</v>
+      </c>
+      <c r="E48">
+        <v>155.734</v>
+      </c>
+      <c r="F48">
+        <v>176.134</v>
+      </c>
+      <c r="G48">
+        <v>42.7</v>
+      </c>
+      <c r="H48">
+        <v>362.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>273.3</v>
+      </c>
+      <c r="K48">
+        <v>13.4</v>
+      </c>
+      <c r="L48">
+        <v>259.9</v>
+      </c>
+      <c r="M48">
+        <v>8.0493238</v>
+      </c>
+      <c r="N48">
+        <v>251.8506762</v>
+      </c>
+      <c r="O48">
+        <v>50.37013524</v>
+      </c>
+      <c r="P48">
+        <v>201.48054096</v>
+      </c>
+      <c r="Q48">
+        <v>214.88054096</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.09877440684324526</v>
+      </c>
+      <c r="T48">
+        <v>0.7512395037362224</v>
+      </c>
+      <c r="U48">
+        <v>0.0457</v>
+      </c>
+      <c r="V48">
+        <v>0.2</v>
+      </c>
+      <c r="W48">
+        <v>0.03656</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>32.28842651354142</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.07006204449778558</v>
+      </c>
+      <c r="C49">
+        <v>206.7693276033571</v>
+      </c>
+      <c r="D49">
+        <v>344.0323276033571</v>
+      </c>
+      <c r="E49">
+        <v>159.563</v>
+      </c>
+      <c r="F49">
+        <v>179.963</v>
+      </c>
+      <c r="G49">
+        <v>42.7</v>
+      </c>
+      <c r="H49">
+        <v>362.5</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>273.3</v>
+      </c>
+      <c r="K49">
+        <v>13.4</v>
+      </c>
+      <c r="L49">
+        <v>259.9</v>
+      </c>
+      <c r="M49">
+        <v>8.224309100000001</v>
+      </c>
+      <c r="N49">
+        <v>251.6756909</v>
+      </c>
+      <c r="O49">
+        <v>50.33513817999999</v>
+      </c>
+      <c r="P49">
+        <v>201.34055272</v>
+      </c>
+      <c r="Q49">
+        <v>214.74055272</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.09977140471280299</v>
+      </c>
+      <c r="T49">
+        <v>0.7637279004403404</v>
+      </c>
+      <c r="U49">
+        <v>0.0457</v>
+      </c>
+      <c r="V49">
+        <v>0.2</v>
+      </c>
+      <c r="W49">
+        <v>0.03656</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>31.60143871538097</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.06996830930021873</v>
+      </c>
+      <c r="C50">
+        <v>203.0193253971759</v>
+      </c>
+      <c r="D50">
+        <v>344.1113253971758</v>
+      </c>
+      <c r="E50">
+        <v>163.392</v>
+      </c>
+      <c r="F50">
+        <v>183.792</v>
+      </c>
+      <c r="G50">
+        <v>42.7</v>
+      </c>
+      <c r="H50">
+        <v>362.5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>273.3</v>
+      </c>
+      <c r="K50">
+        <v>13.4</v>
+      </c>
+      <c r="L50">
+        <v>259.9</v>
+      </c>
+      <c r="M50">
+        <v>8.399294399999999</v>
+      </c>
+      <c r="N50">
+        <v>251.5007056</v>
+      </c>
+      <c r="O50">
+        <v>50.30014111999999</v>
+      </c>
+      <c r="P50">
+        <v>201.20056448</v>
+      </c>
+      <c r="Q50">
+        <v>214.60056448</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1008067486542668</v>
+      </c>
+      <c r="T50">
+        <v>0.7766966200946168</v>
+      </c>
+      <c r="U50">
+        <v>0.0457</v>
+      </c>
+      <c r="V50">
+        <v>0.2</v>
+      </c>
+      <c r="W50">
+        <v>0.03656</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>30.94307540881054</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.06987457410265187</v>
+      </c>
+      <c r="C51">
+        <v>199.269359478775</v>
+      </c>
+      <c r="D51">
+        <v>344.190359478775</v>
+      </c>
+      <c r="E51">
+        <v>167.221</v>
+      </c>
+      <c r="F51">
+        <v>187.621</v>
+      </c>
+      <c r="G51">
+        <v>42.7</v>
+      </c>
+      <c r="H51">
+        <v>362.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>273.3</v>
+      </c>
+      <c r="K51">
+        <v>13.4</v>
+      </c>
+      <c r="L51">
+        <v>259.9</v>
+      </c>
+      <c r="M51">
+        <v>8.5742797</v>
+      </c>
+      <c r="N51">
+        <v>251.3257203</v>
+      </c>
+      <c r="O51">
+        <v>50.26514406</v>
+      </c>
+      <c r="P51">
+        <v>201.06057624</v>
+      </c>
+      <c r="Q51">
+        <v>214.4605762400001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1018826943189252</v>
+      </c>
+      <c r="T51">
+        <v>0.7901739169902374</v>
+      </c>
+      <c r="U51">
+        <v>0.0457</v>
+      </c>
+      <c r="V51">
+        <v>0.2</v>
+      </c>
+      <c r="W51">
+        <v>0.03656</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>30.31158407393685</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.06978083890508502</v>
+      </c>
+      <c r="C52">
+        <v>195.5194298731633</v>
+      </c>
+      <c r="D52">
+        <v>344.2694298731633</v>
+      </c>
+      <c r="E52">
+        <v>171.05</v>
+      </c>
+      <c r="F52">
+        <v>191.45</v>
+      </c>
+      <c r="G52">
+        <v>42.7</v>
+      </c>
+      <c r="H52">
+        <v>362.5</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>273.3</v>
+      </c>
+      <c r="K52">
+        <v>13.4</v>
+      </c>
+      <c r="L52">
+        <v>259.9</v>
+      </c>
+      <c r="M52">
+        <v>8.749265000000001</v>
+      </c>
+      <c r="N52">
+        <v>251.150735</v>
+      </c>
+      <c r="O52">
+        <v>50.230147</v>
+      </c>
+      <c r="P52">
+        <v>200.920588</v>
+      </c>
+      <c r="Q52">
+        <v>214.320588</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.10300167781017</v>
+      </c>
+      <c r="T52">
+        <v>0.8041903057616829</v>
+      </c>
+      <c r="U52">
+        <v>0.0457</v>
+      </c>
+      <c r="V52">
+        <v>0.2</v>
+      </c>
+      <c r="W52">
+        <v>0.03656</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>29.70535239245811</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.06968710370751816</v>
+      </c>
+      <c r="C53">
+        <v>191.769536605373</v>
+      </c>
+      <c r="D53">
+        <v>344.3485366053731</v>
+      </c>
+      <c r="E53">
+        <v>174.879</v>
+      </c>
+      <c r="F53">
+        <v>195.279</v>
+      </c>
+      <c r="G53">
+        <v>42.7</v>
+      </c>
+      <c r="H53">
+        <v>362.5</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>273.3</v>
+      </c>
+      <c r="K53">
+        <v>13.4</v>
+      </c>
+      <c r="L53">
+        <v>259.9</v>
+      </c>
+      <c r="M53">
+        <v>8.924250300000001</v>
+      </c>
+      <c r="N53">
+        <v>250.9757497</v>
+      </c>
+      <c r="O53">
+        <v>50.19514993999999</v>
+      </c>
+      <c r="P53">
+        <v>200.78059976</v>
+      </c>
+      <c r="Q53">
+        <v>214.18059976</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1041663340969758</v>
+      </c>
+      <c r="T53">
+        <v>0.8187787920340037</v>
+      </c>
+      <c r="U53">
+        <v>0.0457</v>
+      </c>
+      <c r="V53">
+        <v>0.2</v>
+      </c>
+      <c r="W53">
+        <v>0.03656</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>29.12289450240991</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.06959336850995129</v>
+      </c>
+      <c r="C54">
+        <v>188.0196797004592</v>
+      </c>
+      <c r="D54">
+        <v>344.4276797004592</v>
+      </c>
+      <c r="E54">
+        <v>178.708</v>
+      </c>
+      <c r="F54">
+        <v>199.108</v>
+      </c>
+      <c r="G54">
+        <v>42.7</v>
+      </c>
+      <c r="H54">
+        <v>362.5</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>273.3</v>
+      </c>
+      <c r="K54">
+        <v>13.4</v>
+      </c>
+      <c r="L54">
+        <v>259.9</v>
+      </c>
+      <c r="M54">
+        <v>9.099235600000002</v>
+      </c>
+      <c r="N54">
+        <v>250.8007644</v>
+      </c>
+      <c r="O54">
+        <v>50.16015287999999</v>
+      </c>
+      <c r="P54">
+        <v>200.64061152</v>
+      </c>
+      <c r="Q54">
+        <v>214.04061152</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1053795177290652</v>
+      </c>
+      <c r="T54">
+        <v>0.8339751319010045</v>
+      </c>
+      <c r="U54">
+        <v>0.0457</v>
+      </c>
+      <c r="V54">
+        <v>0.2</v>
+      </c>
+      <c r="W54">
+        <v>0.03656</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>28.56283883890202</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.06949963331238444</v>
+      </c>
+      <c r="C55">
+        <v>184.2698591834996</v>
+      </c>
+      <c r="D55">
+        <v>344.5068591834997</v>
+      </c>
+      <c r="E55">
+        <v>182.537</v>
+      </c>
+      <c r="F55">
+        <v>202.937</v>
+      </c>
+      <c r="G55">
+        <v>42.7</v>
+      </c>
+      <c r="H55">
+        <v>362.5</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>273.3</v>
+      </c>
+      <c r="K55">
+        <v>13.4</v>
+      </c>
+      <c r="L55">
+        <v>259.9</v>
+      </c>
+      <c r="M55">
+        <v>9.274220900000001</v>
+      </c>
+      <c r="N55">
+        <v>250.6257791</v>
+      </c>
+      <c r="O55">
+        <v>50.12515582</v>
+      </c>
+      <c r="P55">
+        <v>200.50062328</v>
+      </c>
+      <c r="Q55">
+        <v>213.90062328</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1066443261965627</v>
+      </c>
+      <c r="T55">
+        <v>0.8498181245283033</v>
+      </c>
+      <c r="U55">
+        <v>0.0457</v>
+      </c>
+      <c r="V55">
+        <v>0.2</v>
+      </c>
+      <c r="W55">
+        <v>0.03656</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>28.02391735137558</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.06940589811481759</v>
+      </c>
+      <c r="C56">
+        <v>180.5200750795957</v>
+      </c>
+      <c r="D56">
+        <v>344.5860750795957</v>
+      </c>
+      <c r="E56">
+        <v>186.366</v>
+      </c>
+      <c r="F56">
+        <v>206.766</v>
+      </c>
+      <c r="G56">
+        <v>42.7</v>
+      </c>
+      <c r="H56">
+        <v>362.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>273.3</v>
+      </c>
+      <c r="K56">
+        <v>13.4</v>
+      </c>
+      <c r="L56">
+        <v>259.9</v>
+      </c>
+      <c r="M56">
+        <v>9.449206200000001</v>
+      </c>
+      <c r="N56">
+        <v>250.4507938</v>
+      </c>
+      <c r="O56">
+        <v>50.09015875999999</v>
+      </c>
+      <c r="P56">
+        <v>200.36063504</v>
+      </c>
+      <c r="Q56">
+        <v>213.76063504</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.10796412633656</v>
+      </c>
+      <c r="T56">
+        <v>0.8663499429220063</v>
+      </c>
+      <c r="U56">
+        <v>0.0457</v>
+      </c>
+      <c r="V56">
+        <v>0.2</v>
+      </c>
+      <c r="W56">
+        <v>0.03656</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>27.5049559189427</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.06931216291725073</v>
+      </c>
+      <c r="C57">
+        <v>176.7703274138715</v>
+      </c>
+      <c r="D57">
+        <v>344.6653274138715</v>
+      </c>
+      <c r="E57">
+        <v>190.195</v>
+      </c>
+      <c r="F57">
+        <v>210.595</v>
+      </c>
+      <c r="G57">
+        <v>42.7</v>
+      </c>
+      <c r="H57">
+        <v>362.5</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>273.3</v>
+      </c>
+      <c r="K57">
+        <v>13.4</v>
+      </c>
+      <c r="L57">
+        <v>259.9</v>
+      </c>
+      <c r="M57">
+        <v>9.6241915</v>
+      </c>
+      <c r="N57">
+        <v>250.2758085</v>
+      </c>
+      <c r="O57">
+        <v>50.0551617</v>
+      </c>
+      <c r="P57">
+        <v>200.2206468000001</v>
+      </c>
+      <c r="Q57">
+        <v>213.6206468000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1093425842605572</v>
+      </c>
+      <c r="T57">
+        <v>0.883616508799874</v>
+      </c>
+      <c r="U57">
+        <v>0.0457</v>
+      </c>
+      <c r="V57">
+        <v>0.2</v>
+      </c>
+      <c r="W57">
+        <v>0.03656</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>27.00486581132556</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.06921842771968387</v>
+      </c>
+      <c r="C58">
+        <v>173.0206162114744</v>
+      </c>
+      <c r="D58">
+        <v>344.7446162114745</v>
+      </c>
+      <c r="E58">
+        <v>194.024</v>
+      </c>
+      <c r="F58">
+        <v>214.424</v>
+      </c>
+      <c r="G58">
+        <v>42.7</v>
+      </c>
+      <c r="H58">
+        <v>362.5</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>273.3</v>
+      </c>
+      <c r="K58">
+        <v>13.4</v>
+      </c>
+      <c r="L58">
+        <v>259.9</v>
+      </c>
+      <c r="M58">
+        <v>9.799176800000001</v>
+      </c>
+      <c r="N58">
+        <v>250.1008232</v>
+      </c>
+      <c r="O58">
+        <v>50.02016464</v>
+      </c>
+      <c r="P58">
+        <v>200.08065856</v>
+      </c>
+      <c r="Q58">
+        <v>213.4806585600001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1107836993629179</v>
+      </c>
+      <c r="T58">
+        <v>0.9016679185812809</v>
+      </c>
+      <c r="U58">
+        <v>0.0457</v>
+      </c>
+      <c r="V58">
+        <v>0.2</v>
+      </c>
+      <c r="W58">
+        <v>0.03656</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>26.52263606469474</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.06912469252211703</v>
+      </c>
+      <c r="C59">
+        <v>169.270941497575</v>
+      </c>
+      <c r="D59">
+        <v>344.823941497575</v>
+      </c>
+      <c r="E59">
+        <v>197.853</v>
+      </c>
+      <c r="F59">
+        <v>218.253</v>
+      </c>
+      <c r="G59">
+        <v>42.7</v>
+      </c>
+      <c r="H59">
+        <v>362.5</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>273.3</v>
+      </c>
+      <c r="K59">
+        <v>13.4</v>
+      </c>
+      <c r="L59">
+        <v>259.9</v>
+      </c>
+      <c r="M59">
+        <v>9.974162100000001</v>
+      </c>
+      <c r="N59">
+        <v>249.9258379</v>
+      </c>
+      <c r="O59">
+        <v>49.98516758</v>
+      </c>
+      <c r="P59">
+        <v>199.94067032</v>
+      </c>
+      <c r="Q59">
+        <v>213.34067032</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1122918430746908</v>
+      </c>
+      <c r="T59">
+        <v>0.9205589288176372</v>
+      </c>
+      <c r="U59">
+        <v>0.0457</v>
+      </c>
+      <c r="V59">
+        <v>0.2</v>
+      </c>
+      <c r="W59">
+        <v>0.03656</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>26.05732666005098</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.06903095732455017</v>
+      </c>
+      <c r="C60">
+        <v>165.5213032973669</v>
+      </c>
+      <c r="D60">
+        <v>344.9033032973669</v>
+      </c>
+      <c r="E60">
+        <v>201.682</v>
+      </c>
+      <c r="F60">
+        <v>222.082</v>
+      </c>
+      <c r="G60">
+        <v>42.7</v>
+      </c>
+      <c r="H60">
+        <v>362.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>273.3</v>
+      </c>
+      <c r="K60">
+        <v>13.4</v>
+      </c>
+      <c r="L60">
+        <v>259.9</v>
+      </c>
+      <c r="M60">
+        <v>10.1491474</v>
+      </c>
+      <c r="N60">
+        <v>249.7508526</v>
+      </c>
+      <c r="O60">
+        <v>49.95017051999999</v>
+      </c>
+      <c r="P60">
+        <v>199.80068208</v>
+      </c>
+      <c r="Q60">
+        <v>213.20068208</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1138718031536909</v>
+      </c>
+      <c r="T60">
+        <v>0.94034951097001</v>
+      </c>
+      <c r="U60">
+        <v>0.0457</v>
+      </c>
+      <c r="V60">
+        <v>0.2</v>
+      </c>
+      <c r="W60">
+        <v>0.03656</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>25.60806240729148</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.06893722212698332</v>
+      </c>
+      <c r="C61">
+        <v>161.7717016360669</v>
+      </c>
+      <c r="D61">
+        <v>344.9827016360669</v>
+      </c>
+      <c r="E61">
+        <v>205.511</v>
+      </c>
+      <c r="F61">
+        <v>225.911</v>
+      </c>
+      <c r="G61">
+        <v>42.7</v>
+      </c>
+      <c r="H61">
+        <v>362.5</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>273.3</v>
+      </c>
+      <c r="K61">
+        <v>13.4</v>
+      </c>
+      <c r="L61">
+        <v>259.9</v>
+      </c>
+      <c r="M61">
+        <v>10.3241327</v>
+      </c>
+      <c r="N61">
+        <v>249.5758673</v>
+      </c>
+      <c r="O61">
+        <v>49.91517345999999</v>
+      </c>
+      <c r="P61">
+        <v>199.66069384</v>
+      </c>
+      <c r="Q61">
+        <v>213.06069384</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1155288344560569</v>
+      </c>
+      <c r="T61">
+        <v>0.9611054873737186</v>
+      </c>
+      <c r="U61">
+        <v>0.0457</v>
+      </c>
+      <c r="V61">
+        <v>0.2</v>
+      </c>
+      <c r="W61">
+        <v>0.03656</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>25.17402745123569</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.06884348692941646</v>
+      </c>
+      <c r="C62">
+        <v>158.0221365389152</v>
+      </c>
+      <c r="D62">
+        <v>345.0621365389152</v>
+      </c>
+      <c r="E62">
+        <v>209.34</v>
+      </c>
+      <c r="F62">
+        <v>229.74</v>
+      </c>
+      <c r="G62">
+        <v>42.7</v>
+      </c>
+      <c r="H62">
+        <v>362.5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>273.3</v>
+      </c>
+      <c r="K62">
+        <v>13.4</v>
+      </c>
+      <c r="L62">
+        <v>259.9</v>
+      </c>
+      <c r="M62">
+        <v>10.499118</v>
+      </c>
+      <c r="N62">
+        <v>249.400882</v>
+      </c>
+      <c r="O62">
+        <v>49.8801764</v>
+      </c>
+      <c r="P62">
+        <v>199.5207056</v>
+      </c>
+      <c r="Q62">
+        <v>212.9207056</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1172687173235411</v>
+      </c>
+      <c r="T62">
+        <v>0.9828992625976125</v>
+      </c>
+      <c r="U62">
+        <v>0.0457</v>
+      </c>
+      <c r="V62">
+        <v>0.2</v>
+      </c>
+      <c r="W62">
+        <v>0.03656</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>24.75446032704843</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.06874975173184961</v>
+      </c>
+      <c r="C63">
+        <v>154.272608031175</v>
+      </c>
+      <c r="D63">
+        <v>345.141608031175</v>
+      </c>
+      <c r="E63">
+        <v>213.169</v>
+      </c>
+      <c r="F63">
+        <v>233.569</v>
+      </c>
+      <c r="G63">
+        <v>42.7</v>
+      </c>
+      <c r="H63">
+        <v>362.5</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>273.3</v>
+      </c>
+      <c r="K63">
+        <v>13.4</v>
+      </c>
+      <c r="L63">
+        <v>259.9</v>
+      </c>
+      <c r="M63">
+        <v>10.6741033</v>
+      </c>
+      <c r="N63">
+        <v>249.2258967</v>
+      </c>
+      <c r="O63">
+        <v>49.84517933999999</v>
+      </c>
+      <c r="P63">
+        <v>199.38071736</v>
+      </c>
+      <c r="Q63">
+        <v>212.78071736</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1190978249534605</v>
+      </c>
+      <c r="T63">
+        <v>1.005810667320167</v>
+      </c>
+      <c r="U63">
+        <v>0.0457</v>
+      </c>
+      <c r="V63">
+        <v>0.2</v>
+      </c>
+      <c r="W63">
+        <v>0.03656</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>24.34864950201484</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.06865601653428274</v>
+      </c>
+      <c r="C64">
+        <v>150.523116138133</v>
+      </c>
+      <c r="D64">
+        <v>345.221116138133</v>
+      </c>
+      <c r="E64">
+        <v>216.998</v>
+      </c>
+      <c r="F64">
+        <v>237.398</v>
+      </c>
+      <c r="G64">
+        <v>42.7</v>
+      </c>
+      <c r="H64">
+        <v>362.5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>273.3</v>
+      </c>
+      <c r="K64">
+        <v>13.4</v>
+      </c>
+      <c r="L64">
+        <v>259.9</v>
+      </c>
+      <c r="M64">
+        <v>10.8490886</v>
+      </c>
+      <c r="N64">
+        <v>249.0509114</v>
+      </c>
+      <c r="O64">
+        <v>49.81018227999999</v>
+      </c>
+      <c r="P64">
+        <v>199.24072912</v>
+      </c>
+      <c r="Q64">
+        <v>212.64072912</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1210232014060072</v>
+      </c>
+      <c r="T64">
+        <v>1.029927935449173</v>
+      </c>
+      <c r="U64">
+        <v>0.0457</v>
+      </c>
+      <c r="V64">
+        <v>0.2</v>
+      </c>
+      <c r="W64">
+        <v>0.03656</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>23.95592934875654</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.06856228133671589</v>
+      </c>
+      <c r="C65">
+        <v>146.7736608850992</v>
+      </c>
+      <c r="D65">
+        <v>345.3006608850991</v>
+      </c>
+      <c r="E65">
+        <v>220.827</v>
+      </c>
+      <c r="F65">
+        <v>241.227</v>
+      </c>
+      <c r="G65">
+        <v>42.7</v>
+      </c>
+      <c r="H65">
+        <v>362.5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>273.3</v>
+      </c>
+      <c r="K65">
+        <v>13.4</v>
+      </c>
+      <c r="L65">
+        <v>259.9</v>
+      </c>
+      <c r="M65">
+        <v>11.0240739</v>
+      </c>
+      <c r="N65">
+        <v>248.8759261</v>
+      </c>
+      <c r="O65">
+        <v>49.77518522</v>
+      </c>
+      <c r="P65">
+        <v>199.10074088</v>
+      </c>
+      <c r="Q65">
+        <v>212.5007408800001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1230526522613943</v>
+      </c>
+      <c r="T65">
+        <v>1.05534883969326</v>
+      </c>
+      <c r="U65">
+        <v>0.0457</v>
+      </c>
+      <c r="V65">
+        <v>0.2</v>
+      </c>
+      <c r="W65">
+        <v>0.03656</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>23.57567650195088</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.06846854613914904</v>
+      </c>
+      <c r="C66">
+        <v>143.0242422974067</v>
+      </c>
+      <c r="D66">
+        <v>345.3802422974067</v>
+      </c>
+      <c r="E66">
+        <v>224.656</v>
+      </c>
+      <c r="F66">
+        <v>245.056</v>
+      </c>
+      <c r="G66">
+        <v>42.7</v>
+      </c>
+      <c r="H66">
+        <v>362.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>273.3</v>
+      </c>
+      <c r="K66">
+        <v>13.4</v>
+      </c>
+      <c r="L66">
+        <v>259.9</v>
+      </c>
+      <c r="M66">
+        <v>11.1990592</v>
+      </c>
+      <c r="N66">
+        <v>248.7009408</v>
+      </c>
+      <c r="O66">
+        <v>49.74018816</v>
+      </c>
+      <c r="P66">
+        <v>198.96075264</v>
+      </c>
+      <c r="Q66">
+        <v>212.36075264</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1251948503865251</v>
+      </c>
+      <c r="T66">
+        <v>1.082182016395351</v>
+      </c>
+      <c r="U66">
+        <v>0.0457</v>
+      </c>
+      <c r="V66">
+        <v>0.2</v>
+      </c>
+      <c r="W66">
+        <v>0.03656</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>23.2073065566079</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.06837481094158218</v>
+      </c>
+      <c r="C67">
+        <v>139.2748604004122</v>
+      </c>
+      <c r="D67">
+        <v>345.4598604004122</v>
+      </c>
+      <c r="E67">
+        <v>228.485</v>
+      </c>
+      <c r="F67">
+        <v>248.885</v>
+      </c>
+      <c r="G67">
+        <v>42.7</v>
+      </c>
+      <c r="H67">
+        <v>362.5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>273.3</v>
+      </c>
+      <c r="K67">
+        <v>13.4</v>
+      </c>
+      <c r="L67">
+        <v>259.9</v>
+      </c>
+      <c r="M67">
+        <v>11.3740445</v>
+      </c>
+      <c r="N67">
+        <v>248.5259555</v>
+      </c>
+      <c r="O67">
+        <v>49.70519109999999</v>
+      </c>
+      <c r="P67">
+        <v>198.8207644</v>
+      </c>
+      <c r="Q67">
+        <v>212.2207644</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1274594598330919</v>
+      </c>
+      <c r="T67">
+        <v>1.110548517480419</v>
+      </c>
+      <c r="U67">
+        <v>0.0457</v>
+      </c>
+      <c r="V67">
+        <v>0.2</v>
+      </c>
+      <c r="W67">
+        <v>0.03656</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>22.85027107112163</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.06828107574401532</v>
+      </c>
+      <c r="C68">
+        <v>135.5255152194957</v>
+      </c>
+      <c r="D68">
+        <v>345.5395152194957</v>
+      </c>
+      <c r="E68">
+        <v>232.314</v>
+      </c>
+      <c r="F68">
+        <v>252.714</v>
+      </c>
+      <c r="G68">
+        <v>42.7</v>
+      </c>
+      <c r="H68">
+        <v>362.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>273.3</v>
+      </c>
+      <c r="K68">
+        <v>13.4</v>
+      </c>
+      <c r="L68">
+        <v>259.9</v>
+      </c>
+      <c r="M68">
+        <v>11.5490298</v>
+      </c>
+      <c r="N68">
+        <v>248.3509702</v>
+      </c>
+      <c r="O68">
+        <v>49.67019404</v>
+      </c>
+      <c r="P68">
+        <v>198.6807761600001</v>
+      </c>
+      <c r="Q68">
+        <v>212.0807761600001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1298572816000451</v>
+      </c>
+      <c r="T68">
+        <v>1.140583636276374</v>
+      </c>
+      <c r="U68">
+        <v>0.0457</v>
+      </c>
+      <c r="V68">
+        <v>0.2</v>
+      </c>
+      <c r="W68">
+        <v>0.03656</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>22.5040548427713</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.06818734054644847</v>
+      </c>
+      <c r="C69">
+        <v>131.7762067800606</v>
+      </c>
+      <c r="D69">
+        <v>345.6192067800607</v>
+      </c>
+      <c r="E69">
+        <v>236.143</v>
+      </c>
+      <c r="F69">
+        <v>256.543</v>
+      </c>
+      <c r="G69">
+        <v>42.7</v>
+      </c>
+      <c r="H69">
+        <v>362.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>273.3</v>
+      </c>
+      <c r="K69">
+        <v>13.4</v>
+      </c>
+      <c r="L69">
+        <v>259.9</v>
+      </c>
+      <c r="M69">
+        <v>11.7240151</v>
+      </c>
+      <c r="N69">
+        <v>248.1759849</v>
+      </c>
+      <c r="O69">
+        <v>49.63519698</v>
+      </c>
+      <c r="P69">
+        <v>198.54078792</v>
+      </c>
+      <c r="Q69">
+        <v>211.94078792</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1324004258983287</v>
+      </c>
+      <c r="T69">
+        <v>1.172439065302386</v>
+      </c>
+      <c r="U69">
+        <v>0.0457</v>
+      </c>
+      <c r="V69">
+        <v>0.2</v>
+      </c>
+      <c r="W69">
+        <v>0.03656</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>22.16817342720755</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.06809360534888161</v>
+      </c>
+      <c r="C70">
+        <v>128.0269351075339</v>
+      </c>
+      <c r="D70">
+        <v>345.6989351075339</v>
+      </c>
+      <c r="E70">
+        <v>239.972</v>
+      </c>
+      <c r="F70">
+        <v>260.372</v>
+      </c>
+      <c r="G70">
+        <v>42.7</v>
+      </c>
+      <c r="H70">
+        <v>362.5</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>273.3</v>
+      </c>
+      <c r="K70">
+        <v>13.4</v>
+      </c>
+      <c r="L70">
+        <v>259.9</v>
+      </c>
+      <c r="M70">
+        <v>11.8990004</v>
+      </c>
+      <c r="N70">
+        <v>248.0009996</v>
+      </c>
+      <c r="O70">
+        <v>49.60019991999999</v>
+      </c>
+      <c r="P70">
+        <v>198.40079968</v>
+      </c>
+      <c r="Q70">
+        <v>211.80079968</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.135102516715255</v>
+      </c>
+      <c r="T70">
+        <v>1.206285458642524</v>
+      </c>
+      <c r="U70">
+        <v>0.0457</v>
+      </c>
+      <c r="V70">
+        <v>0.2</v>
+      </c>
+      <c r="W70">
+        <v>0.03656</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>21.84217087680743</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.06799987015131476</v>
+      </c>
+      <c r="C71">
+        <v>124.2777002273658</v>
+      </c>
+      <c r="D71">
+        <v>345.7787002273658</v>
+      </c>
+      <c r="E71">
+        <v>243.801</v>
+      </c>
+      <c r="F71">
+        <v>264.201</v>
+      </c>
+      <c r="G71">
+        <v>42.7</v>
+      </c>
+      <c r="H71">
+        <v>362.5</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>273.3</v>
+      </c>
+      <c r="K71">
+        <v>13.4</v>
+      </c>
+      <c r="L71">
+        <v>259.9</v>
+      </c>
+      <c r="M71">
+        <v>12.0739857</v>
+      </c>
+      <c r="N71">
+        <v>247.8260143</v>
+      </c>
+      <c r="O71">
+        <v>49.56520285999999</v>
+      </c>
+      <c r="P71">
+        <v>198.26081144</v>
+      </c>
+      <c r="Q71">
+        <v>211.66081144</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1379789359719831</v>
+      </c>
+      <c r="T71">
+        <v>1.242315490262672</v>
+      </c>
+      <c r="U71">
+        <v>0.0457</v>
+      </c>
+      <c r="V71">
+        <v>0.2</v>
+      </c>
+      <c r="W71">
+        <v>0.03656</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>21.52561767569428</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.06790613495374789</v>
+      </c>
+      <c r="C72">
+        <v>120.52850216503</v>
+      </c>
+      <c r="D72">
+        <v>345.85850216503</v>
+      </c>
+      <c r="E72">
+        <v>247.63</v>
+      </c>
+      <c r="F72">
+        <v>268.03</v>
+      </c>
+      <c r="G72">
+        <v>42.7</v>
+      </c>
+      <c r="H72">
+        <v>362.5</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>273.3</v>
+      </c>
+      <c r="K72">
+        <v>13.4</v>
+      </c>
+      <c r="L72">
+        <v>259.9</v>
+      </c>
+      <c r="M72">
+        <v>12.248971</v>
+      </c>
+      <c r="N72">
+        <v>247.651029</v>
+      </c>
+      <c r="O72">
+        <v>49.53020579999999</v>
+      </c>
+      <c r="P72">
+        <v>198.1208232</v>
+      </c>
+      <c r="Q72">
+        <v>211.5208232</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.141047116512493</v>
+      </c>
+      <c r="T72">
+        <v>1.280747523990829</v>
+      </c>
+      <c r="U72">
+        <v>0.0457</v>
+      </c>
+      <c r="V72">
+        <v>0.2</v>
+      </c>
+      <c r="W72">
+        <v>0.03656</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>21.21810885175579</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.06781239975618104</v>
+      </c>
+      <c r="C73">
+        <v>116.7793409460241</v>
+      </c>
+      <c r="D73">
+        <v>345.9383409460241</v>
+      </c>
+      <c r="E73">
+        <v>251.459</v>
+      </c>
+      <c r="F73">
+        <v>271.859</v>
+      </c>
+      <c r="G73">
+        <v>42.7</v>
+      </c>
+      <c r="H73">
+        <v>362.5</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>273.3</v>
+      </c>
+      <c r="K73">
+        <v>13.4</v>
+      </c>
+      <c r="L73">
+        <v>259.9</v>
+      </c>
+      <c r="M73">
+        <v>12.4239563</v>
+      </c>
+      <c r="N73">
+        <v>247.4760437</v>
+      </c>
+      <c r="O73">
+        <v>49.49520874</v>
+      </c>
+      <c r="P73">
+        <v>197.98083496</v>
+      </c>
+      <c r="Q73">
+        <v>211.38083496</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1443268957109691</v>
+      </c>
+      <c r="T73">
+        <v>1.321830042803686</v>
+      </c>
+      <c r="U73">
+        <v>0.0457</v>
+      </c>
+      <c r="V73">
+        <v>0.2</v>
+      </c>
+      <c r="W73">
+        <v>0.03656</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>20.91926224820994</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.06771866455861419</v>
+      </c>
+      <c r="C74">
+        <v>113.0302165958687</v>
+      </c>
+      <c r="D74">
+        <v>346.0182165958687</v>
+      </c>
+      <c r="E74">
+        <v>255.288</v>
+      </c>
+      <c r="F74">
+        <v>275.688</v>
+      </c>
+      <c r="G74">
+        <v>42.7</v>
+      </c>
+      <c r="H74">
+        <v>362.5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>273.3</v>
+      </c>
+      <c r="K74">
+        <v>13.4</v>
+      </c>
+      <c r="L74">
+        <v>259.9</v>
+      </c>
+      <c r="M74">
+        <v>12.5989416</v>
+      </c>
+      <c r="N74">
+        <v>247.3010584</v>
+      </c>
+      <c r="O74">
+        <v>49.46021168</v>
+      </c>
+      <c r="P74">
+        <v>197.8408467200001</v>
+      </c>
+      <c r="Q74">
+        <v>211.2408467200001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1478409448521935</v>
+      </c>
+      <c r="T74">
+        <v>1.365847027246033</v>
+      </c>
+      <c r="U74">
+        <v>0.0457</v>
+      </c>
+      <c r="V74">
+        <v>0.2</v>
+      </c>
+      <c r="W74">
+        <v>0.03656</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>20.62871693920702</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.06762492936104733</v>
+      </c>
+      <c r="C75">
+        <v>109.2811291401085</v>
+      </c>
+      <c r="D75">
+        <v>346.0981291401085</v>
+      </c>
+      <c r="E75">
+        <v>259.117</v>
+      </c>
+      <c r="F75">
+        <v>279.517</v>
+      </c>
+      <c r="G75">
+        <v>42.7</v>
+      </c>
+      <c r="H75">
+        <v>362.5</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>273.3</v>
+      </c>
+      <c r="K75">
+        <v>13.4</v>
+      </c>
+      <c r="L75">
+        <v>259.9</v>
+      </c>
+      <c r="M75">
+        <v>12.7739269</v>
+      </c>
+      <c r="N75">
+        <v>247.1260731</v>
+      </c>
+      <c r="O75">
+        <v>49.42521462</v>
+      </c>
+      <c r="P75">
+        <v>197.7008584800001</v>
+      </c>
+      <c r="Q75">
+        <v>211.1008584800001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1516152939298049</v>
+      </c>
+      <c r="T75">
+        <v>1.41312452905448</v>
+      </c>
+      <c r="U75">
+        <v>0.0457</v>
+      </c>
+      <c r="V75">
+        <v>0.2</v>
+      </c>
+      <c r="W75">
+        <v>0.03656</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>20.34613177565624</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.06753119416348048</v>
+      </c>
+      <c r="C76">
+        <v>105.5320786043116</v>
+      </c>
+      <c r="D76">
+        <v>346.1780786043116</v>
+      </c>
+      <c r="E76">
+        <v>262.946</v>
+      </c>
+      <c r="F76">
+        <v>283.346</v>
+      </c>
+      <c r="G76">
+        <v>42.7</v>
+      </c>
+      <c r="H76">
+        <v>362.5</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>273.3</v>
+      </c>
+      <c r="K76">
+        <v>13.4</v>
+      </c>
+      <c r="L76">
+        <v>259.9</v>
+      </c>
+      <c r="M76">
+        <v>12.9489122</v>
+      </c>
+      <c r="N76">
+        <v>246.9510878</v>
+      </c>
+      <c r="O76">
+        <v>49.39021756</v>
+      </c>
+      <c r="P76">
+        <v>197.56087024</v>
+      </c>
+      <c r="Q76">
+        <v>210.96087024</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.155679977551848</v>
+      </c>
+      <c r="T76">
+        <v>1.464038761771269</v>
+      </c>
+      <c r="U76">
+        <v>0.0457</v>
+      </c>
+      <c r="V76">
+        <v>0.2</v>
+      </c>
+      <c r="W76">
+        <v>0.03656</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>20.07118404895818</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.06743745896591362</v>
+      </c>
+      <c r="C77">
+        <v>101.7830650140695</v>
+      </c>
+      <c r="D77">
+        <v>346.2580650140694</v>
+      </c>
+      <c r="E77">
+        <v>266.775</v>
+      </c>
+      <c r="F77">
+        <v>287.175</v>
+      </c>
+      <c r="G77">
+        <v>42.7</v>
+      </c>
+      <c r="H77">
+        <v>362.5</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>273.3</v>
+      </c>
+      <c r="K77">
+        <v>13.4</v>
+      </c>
+      <c r="L77">
+        <v>259.9</v>
+      </c>
+      <c r="M77">
+        <v>13.1238975</v>
+      </c>
+      <c r="N77">
+        <v>246.7761025</v>
+      </c>
+      <c r="O77">
+        <v>49.35522049999999</v>
+      </c>
+      <c r="P77">
+        <v>197.420882</v>
+      </c>
+      <c r="Q77">
+        <v>210.820882</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1600698358636545</v>
+      </c>
+      <c r="T77">
+        <v>1.519026133105401</v>
+      </c>
+      <c r="U77">
+        <v>0.0457</v>
+      </c>
+      <c r="V77">
+        <v>0.2</v>
+      </c>
+      <c r="W77">
+        <v>0.03656</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>19.80356826163874</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.06734372376834677</v>
+      </c>
+      <c r="C78">
+        <v>98.03408839499764</v>
+      </c>
+      <c r="D78">
+        <v>346.3380883949976</v>
+      </c>
+      <c r="E78">
+        <v>270.604</v>
+      </c>
+      <c r="F78">
+        <v>291.004</v>
+      </c>
+      <c r="G78">
+        <v>42.7</v>
+      </c>
+      <c r="H78">
+        <v>362.5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>273.3</v>
+      </c>
+      <c r="K78">
+        <v>13.4</v>
+      </c>
+      <c r="L78">
+        <v>259.9</v>
+      </c>
+      <c r="M78">
+        <v>13.2988828</v>
+      </c>
+      <c r="N78">
+        <v>246.6011172</v>
+      </c>
+      <c r="O78">
+        <v>49.32022343999999</v>
+      </c>
+      <c r="P78">
+        <v>197.28089376</v>
+      </c>
+      <c r="Q78">
+        <v>210.68089376</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.1648255157014449</v>
+      </c>
+      <c r="T78">
+        <v>1.578595785384044</v>
+      </c>
+      <c r="U78">
+        <v>0.0457</v>
+      </c>
+      <c r="V78">
+        <v>0.2</v>
+      </c>
+      <c r="W78">
+        <v>0.03656</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>19.54299499503823</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.06724998857077991</v>
+      </c>
+      <c r="C79">
+        <v>94.28514877273506</v>
+      </c>
+      <c r="D79">
+        <v>346.418148772735</v>
+      </c>
+      <c r="E79">
+        <v>274.433</v>
+      </c>
+      <c r="F79">
+        <v>294.833</v>
+      </c>
+      <c r="G79">
+        <v>42.7</v>
+      </c>
+      <c r="H79">
+        <v>362.5</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>273.3</v>
+      </c>
+      <c r="K79">
+        <v>13.4</v>
+      </c>
+      <c r="L79">
+        <v>259.9</v>
+      </c>
+      <c r="M79">
+        <v>13.4738681</v>
+      </c>
+      <c r="N79">
+        <v>246.4261319</v>
+      </c>
+      <c r="O79">
+        <v>49.28522638</v>
+      </c>
+      <c r="P79">
+        <v>197.14090552</v>
+      </c>
+      <c r="Q79">
+        <v>210.5409055200001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.1699947329164344</v>
+      </c>
+      <c r="T79">
+        <v>1.643345407426048</v>
+      </c>
+      <c r="U79">
+        <v>0.0457</v>
+      </c>
+      <c r="V79">
+        <v>0.2</v>
+      </c>
+      <c r="W79">
+        <v>0.03656</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>19.28918986523254</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.06715625337321304</v>
+      </c>
+      <c r="C80">
+        <v>90.53624617294457</v>
+      </c>
+      <c r="D80">
+        <v>346.4982461729446</v>
+      </c>
+      <c r="E80">
+        <v>278.262</v>
+      </c>
+      <c r="F80">
+        <v>298.662</v>
+      </c>
+      <c r="G80">
+        <v>42.7</v>
+      </c>
+      <c r="H80">
+        <v>362.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>273.3</v>
+      </c>
+      <c r="K80">
+        <v>13.4</v>
+      </c>
+      <c r="L80">
+        <v>259.9</v>
+      </c>
+      <c r="M80">
+        <v>13.6488534</v>
+      </c>
+      <c r="N80">
+        <v>246.2511466</v>
+      </c>
+      <c r="O80">
+        <v>49.25022932</v>
+      </c>
+      <c r="P80">
+        <v>197.00091728</v>
+      </c>
+      <c r="Q80">
+        <v>210.40091728</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.1756338789691503</v>
+      </c>
+      <c r="T80">
+        <v>1.713981358744597</v>
+      </c>
+      <c r="U80">
+        <v>0.0457</v>
+      </c>
+      <c r="V80">
+        <v>0.2</v>
+      </c>
+      <c r="W80">
+        <v>0.03656</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>19.04189255926802</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.06706251817564619</v>
+      </c>
+      <c r="C81">
+        <v>86.78738062131271</v>
+      </c>
+      <c r="D81">
+        <v>346.5783806213127</v>
+      </c>
+      <c r="E81">
+        <v>282.091</v>
+      </c>
+      <c r="F81">
+        <v>302.491</v>
+      </c>
+      <c r="G81">
+        <v>42.7</v>
+      </c>
+      <c r="H81">
+        <v>362.5</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>273.3</v>
+      </c>
+      <c r="K81">
+        <v>13.4</v>
+      </c>
+      <c r="L81">
+        <v>259.9</v>
+      </c>
+      <c r="M81">
+        <v>13.8238387</v>
+      </c>
+      <c r="N81">
+        <v>246.0761613</v>
+      </c>
+      <c r="O81">
+        <v>49.21523225999999</v>
+      </c>
+      <c r="P81">
+        <v>196.86092904</v>
+      </c>
+      <c r="Q81">
+        <v>210.26092904</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.1818100865506962</v>
+      </c>
+      <c r="T81">
+        <v>1.791344543522056</v>
+      </c>
+      <c r="U81">
+        <v>0.0457</v>
+      </c>
+      <c r="V81">
+        <v>0.2</v>
+      </c>
+      <c r="W81">
+        <v>0.03656</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>18.80085594459374</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.06696878297807934</v>
+      </c>
+      <c r="C82">
+        <v>83.03855214354957</v>
+      </c>
+      <c r="D82">
+        <v>346.6585521435496</v>
+      </c>
+      <c r="E82">
+        <v>285.92</v>
+      </c>
+      <c r="F82">
+        <v>306.32</v>
+      </c>
+      <c r="G82">
+        <v>42.7</v>
+      </c>
+      <c r="H82">
+        <v>362.5</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>273.3</v>
+      </c>
+      <c r="K82">
+        <v>13.4</v>
+      </c>
+      <c r="L82">
+        <v>259.9</v>
+      </c>
+      <c r="M82">
+        <v>13.998824</v>
+      </c>
+      <c r="N82">
+        <v>245.901176</v>
+      </c>
+      <c r="O82">
+        <v>49.18023519999999</v>
+      </c>
+      <c r="P82">
+        <v>196.7209408</v>
+      </c>
+      <c r="Q82">
+        <v>210.1209408</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.1886039148903967</v>
+      </c>
+      <c r="T82">
+        <v>1.876444046777261</v>
+      </c>
+      <c r="U82">
+        <v>0.0457</v>
+      </c>
+      <c r="V82">
+        <v>0.2</v>
+      </c>
+      <c r="W82">
+        <v>0.03656</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>18.56584524528632</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.06687504778051248</v>
+      </c>
+      <c r="C83">
+        <v>79.28976076538936</v>
+      </c>
+      <c r="D83">
+        <v>346.7387607653894</v>
+      </c>
+      <c r="E83">
+        <v>289.749</v>
+      </c>
+      <c r="F83">
+        <v>310.149</v>
+      </c>
+      <c r="G83">
+        <v>42.7</v>
+      </c>
+      <c r="H83">
+        <v>362.5</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>273.3</v>
+      </c>
+      <c r="K83">
+        <v>13.4</v>
+      </c>
+      <c r="L83">
+        <v>259.9</v>
+      </c>
+      <c r="M83">
+        <v>14.1738093</v>
+      </c>
+      <c r="N83">
+        <v>245.7261907</v>
+      </c>
+      <c r="O83">
+        <v>49.14523813999999</v>
+      </c>
+      <c r="P83">
+        <v>196.58095256</v>
+      </c>
+      <c r="Q83">
+        <v>209.98095256</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.1961128830553289</v>
+      </c>
+      <c r="T83">
+        <v>1.970501392480382</v>
+      </c>
+      <c r="U83">
+        <v>0.0457</v>
+      </c>
+      <c r="V83">
+        <v>0.2</v>
+      </c>
+      <c r="W83">
+        <v>0.03656</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>18.33663727929513</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.06678131258294563</v>
+      </c>
+      <c r="C84">
+        <v>75.54100651258983</v>
+      </c>
+      <c r="D84">
+        <v>346.8190065125899</v>
+      </c>
+      <c r="E84">
+        <v>293.578</v>
+      </c>
+      <c r="F84">
+        <v>313.978</v>
+      </c>
+      <c r="G84">
+        <v>42.7</v>
+      </c>
+      <c r="H84">
+        <v>362.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>273.3</v>
+      </c>
+      <c r="K84">
+        <v>13.4</v>
+      </c>
+      <c r="L84">
+        <v>259.9</v>
+      </c>
+      <c r="M84">
+        <v>14.3487946</v>
+      </c>
+      <c r="N84">
+        <v>245.5512054</v>
+      </c>
+      <c r="O84">
+        <v>49.11024107999999</v>
+      </c>
+      <c r="P84">
+        <v>196.44096432</v>
+      </c>
+      <c r="Q84">
+        <v>209.84096432</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2044561810163647</v>
+      </c>
+      <c r="T84">
+        <v>2.075009554372738</v>
+      </c>
+      <c r="U84">
+        <v>0.0457</v>
+      </c>
+      <c r="V84">
+        <v>0.2</v>
+      </c>
+      <c r="W84">
+        <v>0.03656</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>18.11301975149885</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.06668757738537878</v>
+      </c>
+      <c r="C85">
+        <v>71.79228941093282</v>
+      </c>
+      <c r="D85">
+        <v>346.8992894109329</v>
+      </c>
+      <c r="E85">
+        <v>297.407</v>
+      </c>
+      <c r="F85">
+        <v>317.807</v>
+      </c>
+      <c r="G85">
+        <v>42.7</v>
+      </c>
+      <c r="H85">
+        <v>362.5</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>273.3</v>
+      </c>
+      <c r="K85">
+        <v>13.4</v>
+      </c>
+      <c r="L85">
+        <v>259.9</v>
+      </c>
+      <c r="M85">
+        <v>14.5237799</v>
+      </c>
+      <c r="N85">
+        <v>245.3762201</v>
+      </c>
+      <c r="O85">
+        <v>49.07524402</v>
+      </c>
+      <c r="P85">
+        <v>196.3009760800001</v>
+      </c>
+      <c r="Q85">
+        <v>209.7009760800001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2137810434434047</v>
+      </c>
+      <c r="T85">
+        <v>2.191812794134784</v>
+      </c>
+      <c r="U85">
+        <v>0.0457</v>
+      </c>
+      <c r="V85">
+        <v>0.2</v>
+      </c>
+      <c r="W85">
+        <v>0.03656</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>17.89479059786633</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.06659384218781192</v>
+      </c>
+      <c r="C86">
+        <v>68.04360948622406</v>
+      </c>
+      <c r="D86">
+        <v>346.979609486224</v>
+      </c>
+      <c r="E86">
+        <v>301.236</v>
+      </c>
+      <c r="F86">
+        <v>321.636</v>
+      </c>
+      <c r="G86">
+        <v>42.7</v>
+      </c>
+      <c r="H86">
+        <v>362.5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>273.3</v>
+      </c>
+      <c r="K86">
+        <v>13.4</v>
+      </c>
+      <c r="L86">
+        <v>259.9</v>
+      </c>
+      <c r="M86">
+        <v>14.6987652</v>
+      </c>
+      <c r="N86">
+        <v>245.2012348</v>
+      </c>
+      <c r="O86">
+        <v>49.04024696</v>
+      </c>
+      <c r="P86">
+        <v>196.16098784</v>
+      </c>
+      <c r="Q86">
+        <v>209.5609878400001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2242715136738245</v>
+      </c>
+      <c r="T86">
+        <v>2.323216438867084</v>
+      </c>
+      <c r="U86">
+        <v>0.0457</v>
+      </c>
+      <c r="V86">
+        <v>0.2</v>
+      </c>
+      <c r="W86">
+        <v>0.03656</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>17.68175737646316</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.06650010699024507</v>
+      </c>
+      <c r="C87">
+        <v>64.29496676429278</v>
+      </c>
+      <c r="D87">
+        <v>347.0599667642928</v>
+      </c>
+      <c r="E87">
+        <v>305.065</v>
+      </c>
+      <c r="F87">
+        <v>325.465</v>
+      </c>
+      <c r="G87">
+        <v>42.7</v>
+      </c>
+      <c r="H87">
+        <v>362.5</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>273.3</v>
+      </c>
+      <c r="K87">
+        <v>13.4</v>
+      </c>
+      <c r="L87">
+        <v>259.9</v>
+      </c>
+      <c r="M87">
+        <v>14.8737505</v>
+      </c>
+      <c r="N87">
+        <v>245.0262495</v>
+      </c>
+      <c r="O87">
+        <v>49.0052499</v>
+      </c>
+      <c r="P87">
+        <v>196.0209996</v>
+      </c>
+      <c r="Q87">
+        <v>209.4209996</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.2361607132683004</v>
+      </c>
+      <c r="T87">
+        <v>2.472140569563692</v>
+      </c>
+      <c r="U87">
+        <v>0.0457</v>
+      </c>
+      <c r="V87">
+        <v>0.2</v>
+      </c>
+      <c r="W87">
+        <v>0.03656</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>17.47373670144595</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.06640637179267822</v>
+      </c>
+      <c r="C88">
+        <v>60.54636127099252</v>
+      </c>
+      <c r="D88">
+        <v>347.1403612709925</v>
+      </c>
+      <c r="E88">
+        <v>308.894</v>
+      </c>
+      <c r="F88">
+        <v>329.294</v>
+      </c>
+      <c r="G88">
+        <v>42.7</v>
+      </c>
+      <c r="H88">
+        <v>362.5</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>273.3</v>
+      </c>
+      <c r="K88">
+        <v>13.4</v>
+      </c>
+      <c r="L88">
+        <v>259.9</v>
+      </c>
+      <c r="M88">
+        <v>15.0487358</v>
+      </c>
+      <c r="N88">
+        <v>244.8512642</v>
+      </c>
+      <c r="O88">
+        <v>48.97025283999999</v>
+      </c>
+      <c r="P88">
+        <v>195.88101136</v>
+      </c>
+      <c r="Q88">
+        <v>209.28101136</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.2497483699477015</v>
+      </c>
+      <c r="T88">
+        <v>2.642339576074101</v>
+      </c>
+      <c r="U88">
+        <v>0.0457</v>
+      </c>
+      <c r="V88">
+        <v>0.2</v>
+      </c>
+      <c r="W88">
+        <v>0.03656</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>17.27055371654541</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.06631263659511136</v>
+      </c>
+      <c r="C89">
+        <v>56.79779303220079</v>
+      </c>
+      <c r="D89">
+        <v>347.2207930322008</v>
+      </c>
+      <c r="E89">
+        <v>312.723</v>
+      </c>
+      <c r="F89">
+        <v>333.123</v>
+      </c>
+      <c r="G89">
+        <v>42.7</v>
+      </c>
+      <c r="H89">
+        <v>362.5</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>273.3</v>
+      </c>
+      <c r="K89">
+        <v>13.4</v>
+      </c>
+      <c r="L89">
+        <v>259.9</v>
+      </c>
+      <c r="M89">
+        <v>15.2237211</v>
+      </c>
+      <c r="N89">
+        <v>244.6762789</v>
+      </c>
+      <c r="O89">
+        <v>48.93525577999999</v>
+      </c>
+      <c r="P89">
+        <v>195.74102312</v>
+      </c>
+      <c r="Q89">
+        <v>209.14102312</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.2654264353470104</v>
+      </c>
+      <c r="T89">
+        <v>2.838723045124573</v>
+      </c>
+      <c r="U89">
+        <v>0.0457</v>
+      </c>
+      <c r="V89">
+        <v>0.2</v>
+      </c>
+      <c r="W89">
+        <v>0.03656</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>17.07204160486098</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.06621890139754449</v>
+      </c>
+      <c r="C90">
+        <v>53.04926207381897</v>
+      </c>
+      <c r="D90">
+        <v>347.301262073819</v>
+      </c>
+      <c r="E90">
+        <v>316.552</v>
+      </c>
+      <c r="F90">
+        <v>336.952</v>
+      </c>
+      <c r="G90">
+        <v>42.7</v>
+      </c>
+      <c r="H90">
+        <v>362.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>273.3</v>
+      </c>
+      <c r="K90">
+        <v>13.4</v>
+      </c>
+      <c r="L90">
+        <v>259.9</v>
+      </c>
+      <c r="M90">
+        <v>15.3987064</v>
+      </c>
+      <c r="N90">
+        <v>244.5012936</v>
+      </c>
+      <c r="O90">
+        <v>48.90025872</v>
+      </c>
+      <c r="P90">
+        <v>195.60103488</v>
+      </c>
+      <c r="Q90">
+        <v>209.00103488</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.2837175116462042</v>
+      </c>
+      <c r="T90">
+        <v>3.067837092350124</v>
+      </c>
+      <c r="U90">
+        <v>0.0457</v>
+      </c>
+      <c r="V90">
+        <v>0.2</v>
+      </c>
+      <c r="W90">
+        <v>0.03656</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>16.87804113207847</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.06612516619997764</v>
+      </c>
+      <c r="C91">
+        <v>49.30076842177237</v>
+      </c>
+      <c r="D91">
+        <v>347.3817684217724</v>
+      </c>
+      <c r="E91">
+        <v>320.381</v>
+      </c>
+      <c r="F91">
+        <v>340.781</v>
+      </c>
+      <c r="G91">
+        <v>42.7</v>
+      </c>
+      <c r="H91">
+        <v>362.5</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>273.3</v>
+      </c>
+      <c r="K91">
+        <v>13.4</v>
+      </c>
+      <c r="L91">
+        <v>259.9</v>
+      </c>
+      <c r="M91">
+        <v>15.5736917</v>
+      </c>
+      <c r="N91">
+        <v>244.3263083</v>
+      </c>
+      <c r="O91">
+        <v>48.86526165999999</v>
+      </c>
+      <c r="P91">
+        <v>195.46104664</v>
+      </c>
+      <c r="Q91">
+        <v>208.86104664</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.305334238181615</v>
+      </c>
+      <c r="T91">
+        <v>3.338608239071229</v>
+      </c>
+      <c r="U91">
+        <v>0.0457</v>
+      </c>
+      <c r="V91">
+        <v>0.2</v>
+      </c>
+      <c r="W91">
+        <v>0.03656</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>16.68840022048208</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.0660314310024108</v>
+      </c>
+      <c r="C92">
+        <v>45.55231210201055</v>
+      </c>
+      <c r="D92">
+        <v>347.4623121020106</v>
+      </c>
+      <c r="E92">
+        <v>324.21</v>
+      </c>
+      <c r="F92">
+        <v>344.61</v>
+      </c>
+      <c r="G92">
+        <v>42.7</v>
+      </c>
+      <c r="H92">
+        <v>362.5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>273.3</v>
+      </c>
+      <c r="K92">
+        <v>13.4</v>
+      </c>
+      <c r="L92">
+        <v>259.9</v>
+      </c>
+      <c r="M92">
+        <v>15.748677</v>
+      </c>
+      <c r="N92">
+        <v>244.151323</v>
+      </c>
+      <c r="O92">
+        <v>48.83026459999999</v>
+      </c>
+      <c r="P92">
+        <v>195.3210584</v>
+      </c>
+      <c r="Q92">
+        <v>208.7210584</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.331274310024108</v>
+      </c>
+      <c r="T92">
+        <v>3.663533615136557</v>
+      </c>
+      <c r="U92">
+        <v>0.0457</v>
+      </c>
+      <c r="V92">
+        <v>0.2</v>
+      </c>
+      <c r="W92">
+        <v>0.03656</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>16.50297355136561</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.06593769580484393</v>
+      </c>
+      <c r="C93">
+        <v>41.80389314050711</v>
+      </c>
+      <c r="D93">
+        <v>347.5428931405071</v>
+      </c>
+      <c r="E93">
+        <v>328.039</v>
+      </c>
+      <c r="F93">
+        <v>348.439</v>
+      </c>
+      <c r="G93">
+        <v>42.7</v>
+      </c>
+      <c r="H93">
+        <v>362.5</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>273.3</v>
+      </c>
+      <c r="K93">
+        <v>13.4</v>
+      </c>
+      <c r="L93">
+        <v>259.9</v>
+      </c>
+      <c r="M93">
+        <v>15.9236623</v>
+      </c>
+      <c r="N93">
+        <v>243.9763377</v>
+      </c>
+      <c r="O93">
+        <v>48.79526754</v>
+      </c>
+      <c r="P93">
+        <v>195.18107016</v>
+      </c>
+      <c r="Q93">
+        <v>208.5810701600001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.3629788422760438</v>
+      </c>
+      <c r="T93">
+        <v>4.060664630327511</v>
+      </c>
+      <c r="U93">
+        <v>0.0457</v>
+      </c>
+      <c r="V93">
+        <v>0.2</v>
+      </c>
+      <c r="W93">
+        <v>0.03656</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>16.32162219365831</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.06584396060727708</v>
+      </c>
+      <c r="C94">
+        <v>38.05551156325942</v>
+      </c>
+      <c r="D94">
+        <v>347.6235115632594</v>
+      </c>
+      <c r="E94">
+        <v>331.868</v>
+      </c>
+      <c r="F94">
+        <v>352.268</v>
+      </c>
+      <c r="G94">
+        <v>42.7</v>
+      </c>
+      <c r="H94">
+        <v>362.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>273.3</v>
+      </c>
+      <c r="K94">
+        <v>13.4</v>
+      </c>
+      <c r="L94">
+        <v>259.9</v>
+      </c>
+      <c r="M94">
+        <v>16.0986476</v>
+      </c>
+      <c r="N94">
+        <v>243.8013524</v>
+      </c>
+      <c r="O94">
+        <v>48.76027048</v>
+      </c>
+      <c r="P94">
+        <v>195.04108192</v>
+      </c>
+      <c r="Q94">
+        <v>208.44108192</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.4026095075909636</v>
+      </c>
+      <c r="T94">
+        <v>4.557078399316206</v>
+      </c>
+      <c r="U94">
+        <v>0.0457</v>
+      </c>
+      <c r="V94">
+        <v>0.2</v>
+      </c>
+      <c r="W94">
+        <v>0.03656</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>16.14421325677071</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.06575022540971022</v>
+      </c>
+      <c r="C95">
+        <v>34.30716739628946</v>
+      </c>
+      <c r="D95">
+        <v>347.7041673962894</v>
+      </c>
+      <c r="E95">
+        <v>335.697</v>
+      </c>
+      <c r="F95">
+        <v>356.097</v>
+      </c>
+      <c r="G95">
+        <v>42.7</v>
+      </c>
+      <c r="H95">
+        <v>362.5</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>273.3</v>
+      </c>
+      <c r="K95">
+        <v>13.4</v>
+      </c>
+      <c r="L95">
+        <v>259.9</v>
+      </c>
+      <c r="M95">
+        <v>16.2736329</v>
+      </c>
+      <c r="N95">
+        <v>243.6263671</v>
+      </c>
+      <c r="O95">
+        <v>48.72527341999999</v>
+      </c>
+      <c r="P95">
+        <v>194.90109368</v>
+      </c>
+      <c r="Q95">
+        <v>208.30109368</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.4535632201387177</v>
+      </c>
+      <c r="T95">
+        <v>5.195324673730241</v>
+      </c>
+      <c r="U95">
+        <v>0.0457</v>
+      </c>
+      <c r="V95">
+        <v>0.2</v>
+      </c>
+      <c r="W95">
+        <v>0.03656</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>15.9706195658377</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.06565649021214337</v>
+      </c>
+      <c r="C96">
+        <v>30.55886066564307</v>
+      </c>
+      <c r="D96">
+        <v>347.7848606656431</v>
+      </c>
+      <c r="E96">
+        <v>339.526</v>
+      </c>
+      <c r="F96">
+        <v>359.926</v>
+      </c>
+      <c r="G96">
+        <v>42.7</v>
+      </c>
+      <c r="H96">
+        <v>362.5</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>273.3</v>
+      </c>
+      <c r="K96">
+        <v>13.4</v>
+      </c>
+      <c r="L96">
+        <v>259.9</v>
+      </c>
+      <c r="M96">
+        <v>16.4486182</v>
+      </c>
+      <c r="N96">
+        <v>243.4513818</v>
+      </c>
+      <c r="O96">
+        <v>48.69027636</v>
+      </c>
+      <c r="P96">
+        <v>194.7611054400001</v>
+      </c>
+      <c r="Q96">
+        <v>208.1611054400001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.5215015035357232</v>
+      </c>
+      <c r="T96">
+        <v>6.046319706282288</v>
+      </c>
+      <c r="U96">
+        <v>0.0457</v>
+      </c>
+      <c r="V96">
+        <v>0.2</v>
+      </c>
+      <c r="W96">
+        <v>0.03656</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>15.80071935769048</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.06556275501457651</v>
+      </c>
+      <c r="C97">
+        <v>26.81059139739028</v>
+      </c>
+      <c r="D97">
+        <v>347.8655913973903</v>
+      </c>
+      <c r="E97">
+        <v>343.355</v>
+      </c>
+      <c r="F97">
+        <v>363.755</v>
+      </c>
+      <c r="G97">
+        <v>42.7</v>
+      </c>
+      <c r="H97">
+        <v>362.5</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>273.3</v>
+      </c>
+      <c r="K97">
+        <v>13.4</v>
+      </c>
+      <c r="L97">
+        <v>259.9</v>
+      </c>
+      <c r="M97">
+        <v>16.6236035</v>
+      </c>
+      <c r="N97">
+        <v>243.2763965</v>
+      </c>
+      <c r="O97">
+        <v>48.6552793</v>
+      </c>
+      <c r="P97">
+        <v>194.6211172</v>
+      </c>
+      <c r="Q97">
+        <v>208.0211172</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.616615100291531</v>
+      </c>
+      <c r="T97">
+        <v>7.237712751855157</v>
+      </c>
+      <c r="U97">
+        <v>0.0457</v>
+      </c>
+      <c r="V97">
+        <v>0.2</v>
+      </c>
+      <c r="W97">
+        <v>0.03656</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>15.63439599603058</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.06546901981700966</v>
+      </c>
+      <c r="C98">
+        <v>23.06235961762559</v>
+      </c>
+      <c r="D98">
+        <v>347.9463596176255</v>
+      </c>
+      <c r="E98">
+        <v>347.184</v>
+      </c>
+      <c r="F98">
+        <v>367.5839999999999</v>
+      </c>
+      <c r="G98">
+        <v>42.7</v>
+      </c>
+      <c r="H98">
+        <v>362.5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>273.3</v>
+      </c>
+      <c r="K98">
+        <v>13.4</v>
+      </c>
+      <c r="L98">
+        <v>259.9</v>
+      </c>
+      <c r="M98">
+        <v>16.7985888</v>
+      </c>
+      <c r="N98">
+        <v>243.1014112</v>
+      </c>
+      <c r="O98">
+        <v>48.62028223999999</v>
+      </c>
+      <c r="P98">
+        <v>194.48112896</v>
+      </c>
+      <c r="Q98">
+        <v>207.88112896</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>0.7592854954252408</v>
+      </c>
+      <c r="T98">
+        <v>9.024802320214436</v>
+      </c>
+      <c r="U98">
+        <v>0.0457</v>
+      </c>
+      <c r="V98">
+        <v>0.2</v>
+      </c>
+      <c r="W98">
+        <v>0.03656</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>15.47153770440527</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.06537528461944281</v>
+      </c>
+      <c r="C99">
+        <v>19.3141653524674</v>
+      </c>
+      <c r="D99">
+        <v>348.0271653524674</v>
+      </c>
+      <c r="E99">
+        <v>351.013</v>
+      </c>
+      <c r="F99">
+        <v>371.413</v>
+      </c>
+      <c r="G99">
+        <v>42.7</v>
+      </c>
+      <c r="H99">
+        <v>362.5</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>273.3</v>
+      </c>
+      <c r="K99">
+        <v>13.4</v>
+      </c>
+      <c r="L99">
+        <v>259.9</v>
+      </c>
+      <c r="M99">
+        <v>16.9735741</v>
+      </c>
+      <c r="N99">
+        <v>242.9264259</v>
+      </c>
+      <c r="O99">
+        <v>48.58528517999999</v>
+      </c>
+      <c r="P99">
+        <v>194.34114072</v>
+      </c>
+      <c r="Q99">
+        <v>207.74114072</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>0.9970694873147592</v>
+      </c>
+      <c r="T99">
+        <v>12.00328493414659</v>
+      </c>
+      <c r="U99">
+        <v>0.0457</v>
+      </c>
+      <c r="V99">
+        <v>0.2</v>
+      </c>
+      <c r="W99">
+        <v>0.03656</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>15.31203731570006</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.06528154942187595</v>
+      </c>
+      <c r="C100">
+        <v>15.56600862805851</v>
+      </c>
+      <c r="D100">
+        <v>348.1080086280585</v>
+      </c>
+      <c r="E100">
+        <v>354.842</v>
+      </c>
+      <c r="F100">
+        <v>375.242</v>
+      </c>
+      <c r="G100">
+        <v>42.7</v>
+      </c>
+      <c r="H100">
+        <v>362.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>273.3</v>
+      </c>
+      <c r="K100">
+        <v>13.4</v>
+      </c>
+      <c r="L100">
+        <v>259.9</v>
+      </c>
+      <c r="M100">
+        <v>17.1485594</v>
+      </c>
+      <c r="N100">
+        <v>242.7514406</v>
+      </c>
+      <c r="O100">
+        <v>48.55028811999999</v>
+      </c>
+      <c r="P100">
+        <v>194.20115248</v>
+      </c>
+      <c r="Q100">
+        <v>207.60115248</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>1.472637471093796</v>
+      </c>
+      <c r="T100">
+        <v>17.9602501620109</v>
+      </c>
+      <c r="U100">
+        <v>0.0457</v>
+      </c>
+      <c r="V100">
+        <v>0.2</v>
+      </c>
+      <c r="W100">
+        <v>0.03656</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>15.15579203696842</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.0651878142243091</v>
+      </c>
+      <c r="C101">
+        <v>11.81788947056606</v>
+      </c>
+      <c r="D101">
+        <v>348.188889470566</v>
+      </c>
+      <c r="E101">
+        <v>358.671</v>
+      </c>
+      <c r="F101">
+        <v>379.071</v>
+      </c>
+      <c r="G101">
+        <v>42.7</v>
+      </c>
+      <c r="H101">
+        <v>362.5</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>273.3</v>
+      </c>
+      <c r="K101">
+        <v>13.4</v>
+      </c>
+      <c r="L101">
+        <v>259.9</v>
+      </c>
+      <c r="M101">
+        <v>17.3235447</v>
+      </c>
+      <c r="N101">
+        <v>242.5764553</v>
+      </c>
+      <c r="O101">
+        <v>48.51529106</v>
+      </c>
+      <c r="P101">
+        <v>194.06116424</v>
+      </c>
+      <c r="Q101">
+        <v>207.46116424</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>2.899341422430906</v>
+      </c>
+      <c r="T101">
+        <v>35.83114584560384</v>
+      </c>
+      <c r="U101">
+        <v>0.0457</v>
+      </c>
+      <c r="V101">
+        <v>0.2</v>
+      </c>
+      <c r="W101">
+        <v>0.03656</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>15.0027032285142</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
